--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719590</v>
+        <v>119714038</v>
       </c>
       <c r="B11" t="n">
-        <v>91185</v>
+        <v>91884</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547449</v>
+        <v>547465</v>
       </c>
       <c r="R11" t="n">
-        <v>6511879</v>
+        <v>6511856</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119714038</v>
+        <v>119719590</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>91185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>6031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547465</v>
+        <v>547449</v>
       </c>
       <c r="R14" t="n">
-        <v>6511856</v>
+        <v>6511879</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -3213,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119719441</v>
+        <v>119714125</v>
       </c>
       <c r="B26" t="n">
-        <v>8432</v>
+        <v>90966</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,39 +3229,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547507</v>
+        <v>547511</v>
       </c>
       <c r="R26" t="n">
-        <v>6511795</v>
+        <v>6511918</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119714125</v>
+        <v>119719458</v>
       </c>
       <c r="B27" t="n">
-        <v>90966</v>
+        <v>91884</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3332,38 +3327,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5420</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547511</v>
+        <v>547493</v>
       </c>
       <c r="R27" t="n">
-        <v>6511918</v>
+        <v>6511831</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119719458</v>
+        <v>119719441</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>8432</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3434,38 +3429,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547493</v>
+        <v>547507</v>
       </c>
       <c r="R28" t="n">
-        <v>6511831</v>
+        <v>6511795</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119706924</v>
+        <v>119706876</v>
       </c>
       <c r="B5" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547441</v>
+        <v>547406</v>
       </c>
       <c r="R5" t="n">
-        <v>6511942</v>
+        <v>6511956</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119706876</v>
+        <v>119706924</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547406</v>
+        <v>547441</v>
       </c>
       <c r="R6" t="n">
-        <v>6511956</v>
+        <v>6511942</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713966</v>
+        <v>119715785</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1260,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Kvarnsjön, Kvarnsjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547469</v>
+        <v>547377</v>
       </c>
       <c r="R7" t="n">
-        <v>6511781</v>
+        <v>6511828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119715959</v>
+        <v>119713966</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,47 +1362,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547424</v>
+        <v>547469</v>
       </c>
       <c r="R8" t="n">
-        <v>6511904</v>
+        <v>6511781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119716231</v>
+        <v>119714934</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,38 +1464,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547390</v>
+        <v>547481</v>
       </c>
       <c r="R9" t="n">
-        <v>6511934</v>
+        <v>6511713</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119715785</v>
+        <v>119713893</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>91185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,38 +1566,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnsjön, Kvarnsjön, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547377</v>
+        <v>547450</v>
       </c>
       <c r="R10" t="n">
-        <v>6511828</v>
+        <v>6511948</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119714038</v>
+        <v>119719590</v>
       </c>
       <c r="B11" t="n">
-        <v>91884</v>
+        <v>91185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1668,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547465</v>
+        <v>547449</v>
       </c>
       <c r="R11" t="n">
-        <v>6511856</v>
+        <v>6511879</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119715855</v>
+        <v>119719458</v>
       </c>
       <c r="B12" t="n">
-        <v>91182</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,25 +1770,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1339</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547401</v>
+        <v>547493</v>
       </c>
       <c r="R12" t="n">
-        <v>6511820</v>
+        <v>6511831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119715352</v>
+        <v>119719483</v>
       </c>
       <c r="B13" t="n">
-        <v>94681</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547433</v>
+        <v>547493</v>
       </c>
       <c r="R13" t="n">
-        <v>6511757</v>
+        <v>6511831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119719590</v>
+        <v>119715947</v>
       </c>
       <c r="B14" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,38 +1974,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547449</v>
+        <v>547431</v>
       </c>
       <c r="R14" t="n">
-        <v>6511879</v>
+        <v>6511901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119715890</v>
+        <v>119714125</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>90966</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547424</v>
+        <v>547511</v>
       </c>
       <c r="R15" t="n">
-        <v>6511854</v>
+        <v>6511918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119716007</v>
+        <v>119719507</v>
       </c>
       <c r="B16" t="n">
         <v>91884</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547408</v>
+        <v>547463</v>
       </c>
       <c r="R16" t="n">
-        <v>6511895</v>
+        <v>6511851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119716041</v>
+        <v>119715980</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547419</v>
+        <v>547406</v>
       </c>
       <c r="R17" t="n">
-        <v>6511911</v>
+        <v>6511874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119713893</v>
+        <v>119714119</v>
       </c>
       <c r="B18" t="n">
         <v>91185</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547450</v>
+        <v>547512</v>
       </c>
       <c r="R18" t="n">
-        <v>6511948</v>
+        <v>6511928</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119716305</v>
+        <v>119719441</v>
       </c>
       <c r="B19" t="n">
-        <v>94681</v>
+        <v>8432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,34 +2497,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547559</v>
+        <v>547507</v>
       </c>
       <c r="R19" t="n">
-        <v>6511883</v>
+        <v>6511795</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119715929</v>
+        <v>119717409</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,47 +2600,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547424</v>
+        <v>547484</v>
       </c>
       <c r="R20" t="n">
-        <v>6511875</v>
+        <v>6512006</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119715980</v>
+        <v>119716241</v>
       </c>
       <c r="B21" t="n">
-        <v>94681</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2706,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2730,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547406</v>
+        <v>547391</v>
       </c>
       <c r="R21" t="n">
-        <v>6511874</v>
+        <v>6511960</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2796,10 +2792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119714934</v>
+        <v>119714038</v>
       </c>
       <c r="B22" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2808,38 +2804,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547481</v>
+        <v>547465</v>
       </c>
       <c r="R22" t="n">
-        <v>6511713</v>
+        <v>6511856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,10 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119714119</v>
+        <v>119716041</v>
       </c>
       <c r="B23" t="n">
-        <v>91185</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2914,21 +2910,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2938,10 +2934,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547512</v>
+        <v>547419</v>
       </c>
       <c r="R23" t="n">
-        <v>6511928</v>
+        <v>6511911</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3000,10 +2996,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119715947</v>
+        <v>119716305</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,47 +3008,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547431</v>
+        <v>547559</v>
       </c>
       <c r="R24" t="n">
-        <v>6511901</v>
+        <v>6511883</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119719507</v>
+        <v>119715929</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,38 +3110,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547463</v>
+        <v>547424</v>
       </c>
       <c r="R25" t="n">
-        <v>6511851</v>
+        <v>6511875</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119714125</v>
+        <v>119716231</v>
       </c>
       <c r="B26" t="n">
-        <v>90966</v>
+        <v>91884</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3225,25 +3221,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5420</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3249,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547511</v>
+        <v>547390</v>
       </c>
       <c r="R26" t="n">
-        <v>6511918</v>
+        <v>6511934</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3315,7 +3311,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119719458</v>
+        <v>119716007</v>
       </c>
       <c r="B27" t="n">
         <v>91884</v>
@@ -3351,14 +3347,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547493</v>
+        <v>547408</v>
       </c>
       <c r="R27" t="n">
-        <v>6511831</v>
+        <v>6511895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,10 +3413,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119719441</v>
+        <v>119715352</v>
       </c>
       <c r="B28" t="n">
-        <v>8432</v>
+        <v>94681</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,39 +3429,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547507</v>
+        <v>547433</v>
       </c>
       <c r="R28" t="n">
-        <v>6511795</v>
+        <v>6511757</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,10 +3515,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119719483</v>
+        <v>119716135</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,34 +3531,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547493</v>
+        <v>547425</v>
       </c>
       <c r="R29" t="n">
-        <v>6511831</v>
+        <v>6511932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,10 +3617,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119717214</v>
+        <v>119715855</v>
       </c>
       <c r="B30" t="n">
-        <v>94681</v>
+        <v>91182</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,34 +3633,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>1339</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547509</v>
+        <v>547401</v>
       </c>
       <c r="R30" t="n">
-        <v>6511986</v>
+        <v>6511820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,10 +3719,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119716241</v>
+        <v>119715890</v>
       </c>
       <c r="B31" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3740,25 +3731,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3759,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547391</v>
+        <v>547424</v>
       </c>
       <c r="R31" t="n">
-        <v>6511960</v>
+        <v>6511854</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,10 +3821,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119717409</v>
+        <v>119715959</v>
       </c>
       <c r="B32" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3842,38 +3833,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547484</v>
+        <v>547424</v>
       </c>
       <c r="R32" t="n">
-        <v>6512006</v>
+        <v>6511904</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119716135</v>
+        <v>119717214</v>
       </c>
       <c r="B33" t="n">
         <v>94681</v>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547425</v>
+        <v>547509</v>
       </c>
       <c r="R33" t="n">
-        <v>6511932</v>
+        <v>6511986</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,6 +4031,636 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120116625</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Åfallet SV 418 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>547469</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6511866</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120116586</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91185</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Åfallet SV 430 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>547434</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6511887</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120116608</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Åfallet SV 420 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>547447</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6511886</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120116681</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Åfallet SV 435 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>547456</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6511852</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120116696</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Åfallet SV 425 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>547490</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6511838</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -3821,10 +3821,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119715959</v>
+        <v>119717214</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3833,47 +3833,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547424</v>
+        <v>547509</v>
       </c>
       <c r="R32" t="n">
-        <v>6511904</v>
+        <v>6511986</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,10 +3923,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119717214</v>
+        <v>119715959</v>
       </c>
       <c r="B33" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3944,38 +3935,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547509</v>
+        <v>547424</v>
       </c>
       <c r="R33" t="n">
-        <v>6511986</v>
+        <v>6511904</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119715785</v>
+        <v>119717409</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>91884</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,34 +1264,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarnsjön, Kvarnsjön, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547377</v>
+        <v>547484</v>
       </c>
       <c r="R7" t="n">
-        <v>6511828</v>
+        <v>6512006</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713966</v>
+        <v>119715980</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,34 +1366,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547469</v>
+        <v>547406</v>
       </c>
       <c r="R8" t="n">
-        <v>6511781</v>
+        <v>6511874</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713893</v>
+        <v>119716041</v>
       </c>
       <c r="B10" t="n">
-        <v>91185</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,21 +1570,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547450</v>
+        <v>547419</v>
       </c>
       <c r="R10" t="n">
-        <v>6511948</v>
+        <v>6511911</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719590</v>
+        <v>119714119</v>
       </c>
       <c r="B11" t="n">
         <v>91185</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547449</v>
+        <v>547512</v>
       </c>
       <c r="R11" t="n">
-        <v>6511879</v>
+        <v>6511928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719458</v>
+        <v>119719483</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,25 +1770,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119719483</v>
+        <v>119719441</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,34 +1876,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547493</v>
+        <v>547507</v>
       </c>
       <c r="R13" t="n">
-        <v>6511831</v>
+        <v>6511795</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119715947</v>
+        <v>119716007</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,47 +1979,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547431</v>
+        <v>547408</v>
       </c>
       <c r="R14" t="n">
-        <v>6511901</v>
+        <v>6511895</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119714125</v>
+        <v>119713893</v>
       </c>
       <c r="B15" t="n">
-        <v>90966</v>
+        <v>91185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,21 +2085,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>6031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547511</v>
+        <v>547450</v>
       </c>
       <c r="R15" t="n">
-        <v>6511918</v>
+        <v>6511948</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2171,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119719507</v>
+        <v>119716231</v>
       </c>
       <c r="B16" t="n">
         <v>91884</v>
@@ -2215,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547463</v>
+        <v>547390</v>
       </c>
       <c r="R16" t="n">
-        <v>6511851</v>
+        <v>6511934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119715980</v>
+        <v>119715929</v>
       </c>
       <c r="B17" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,38 +2285,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547406</v>
+        <v>547424</v>
       </c>
       <c r="R17" t="n">
-        <v>6511874</v>
+        <v>6511875</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119714119</v>
+        <v>119715947</v>
       </c>
       <c r="B18" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,38 +2396,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547512</v>
+        <v>547431</v>
       </c>
       <c r="R18" t="n">
-        <v>6511928</v>
+        <v>6511901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119719441</v>
+        <v>119714125</v>
       </c>
       <c r="B19" t="n">
-        <v>8432</v>
+        <v>90966</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,39 +2511,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547507</v>
+        <v>547511</v>
       </c>
       <c r="R19" t="n">
-        <v>6511795</v>
+        <v>6511918</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2597,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119717409</v>
+        <v>119713966</v>
       </c>
       <c r="B20" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,38 +2609,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547484</v>
+        <v>547469</v>
       </c>
       <c r="R20" t="n">
-        <v>6512006</v>
+        <v>6511781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,10 +2699,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119716241</v>
+        <v>119715890</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,25 +2711,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547391</v>
+        <v>547424</v>
       </c>
       <c r="R21" t="n">
-        <v>6511960</v>
+        <v>6511854</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2792,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119714038</v>
+        <v>119715352</v>
       </c>
       <c r="B22" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2804,38 +2813,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547465</v>
+        <v>547433</v>
       </c>
       <c r="R22" t="n">
-        <v>6511856</v>
+        <v>6511757</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,10 +2903,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119716041</v>
+        <v>119717214</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,21 +2919,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2934,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547419</v>
+        <v>547509</v>
       </c>
       <c r="R23" t="n">
-        <v>6511911</v>
+        <v>6511986</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119716305</v>
+        <v>119715785</v>
       </c>
       <c r="B24" t="n">
-        <v>94681</v>
+        <v>90562</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3008,38 +3017,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Kvarnsjön, Kvarnsjön, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547559</v>
+        <v>547377</v>
       </c>
       <c r="R24" t="n">
-        <v>6511883</v>
+        <v>6511828</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3098,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119715929</v>
+        <v>119719507</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3110,47 +3119,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547424</v>
+        <v>547463</v>
       </c>
       <c r="R25" t="n">
-        <v>6511875</v>
+        <v>6511851</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,7 +3209,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119716231</v>
+        <v>119714038</v>
       </c>
       <c r="B26" t="n">
         <v>91884</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547390</v>
+        <v>547465</v>
       </c>
       <c r="R26" t="n">
-        <v>6511934</v>
+        <v>6511856</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119716007</v>
+        <v>119715959</v>
       </c>
       <c r="B27" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3323,38 +3323,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547408</v>
+        <v>547424</v>
       </c>
       <c r="R27" t="n">
-        <v>6511895</v>
+        <v>6511904</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119715352</v>
+        <v>119715855</v>
       </c>
       <c r="B28" t="n">
-        <v>94681</v>
+        <v>91182</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3429,21 +3438,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>1339</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3453,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547433</v>
+        <v>547401</v>
       </c>
       <c r="R28" t="n">
-        <v>6511757</v>
+        <v>6511820</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119716135</v>
+        <v>119716241</v>
       </c>
       <c r="B29" t="n">
-        <v>94681</v>
+        <v>90527</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3531,21 +3540,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3555,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547425</v>
+        <v>547391</v>
       </c>
       <c r="R29" t="n">
-        <v>6511932</v>
+        <v>6511960</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3617,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119715855</v>
+        <v>119716135</v>
       </c>
       <c r="B30" t="n">
-        <v>91182</v>
+        <v>94681</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,34 +3642,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1339</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547401</v>
+        <v>547425</v>
       </c>
       <c r="R30" t="n">
-        <v>6511820</v>
+        <v>6511932</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,10 +3728,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119715890</v>
+        <v>119719458</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3731,38 +3740,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547424</v>
+        <v>547493</v>
       </c>
       <c r="R31" t="n">
-        <v>6511854</v>
+        <v>6511831</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3821,7 +3830,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119717214</v>
+        <v>119716305</v>
       </c>
       <c r="B32" t="n">
         <v>94681</v>
@@ -3857,14 +3866,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547509</v>
+        <v>547559</v>
       </c>
       <c r="R32" t="n">
-        <v>6511986</v>
+        <v>6511883</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119715959</v>
+        <v>119719590</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3935,47 +3944,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547424</v>
+        <v>547449</v>
       </c>
       <c r="R33" t="n">
-        <v>6511904</v>
+        <v>6511879</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120116625</v>
+        <v>120116608</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4086,14 +4086,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åfallet SV 418 m, Ög</t>
+          <t>Åfallet SV 420 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547469</v>
+        <v>547447</v>
       </c>
       <c r="R34" t="n">
-        <v>6511866</v>
+        <v>6511886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4126,11 +4126,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4163,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120116586</v>
+        <v>120116681</v>
       </c>
       <c r="B35" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,52 +4170,57 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åfallet SV 430 m, Ög</t>
+          <t>Åfallet SV 435 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547434</v>
+        <v>547456</v>
       </c>
       <c r="R35" t="n">
-        <v>6511887</v>
+        <v>6511852</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4250,6 +4250,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,10 +4287,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120116608</v>
+        <v>120116586</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4294,57 +4299,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åfallet SV 420 m, Ög</t>
+          <t>Åfallet SV 430 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547447</v>
+        <v>547434</v>
       </c>
       <c r="R36" t="n">
-        <v>6511886</v>
+        <v>6511887</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120116681</v>
+        <v>120116625</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4458,14 +4458,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åfallet SV 435 m, Ög</t>
+          <t>Åfallet SV 418 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547456</v>
+        <v>547469</v>
       </c>
       <c r="R37" t="n">
-        <v>6511852</v>
+        <v>6511866</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -1554,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119716041</v>
+        <v>119714119</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>91185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,21 +1570,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547419</v>
+        <v>547512</v>
       </c>
       <c r="R10" t="n">
-        <v>6511911</v>
+        <v>6511928</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119714119</v>
+        <v>119716041</v>
       </c>
       <c r="B11" t="n">
-        <v>91185</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547512</v>
+        <v>547419</v>
       </c>
       <c r="R11" t="n">
-        <v>6511928</v>
+        <v>6511911</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119706876</v>
+        <v>119706924</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>94681</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547406</v>
+        <v>547441</v>
       </c>
       <c r="R5" t="n">
-        <v>6511956</v>
+        <v>6511942</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119706924</v>
+        <v>119706876</v>
       </c>
       <c r="B6" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547441</v>
+        <v>547406</v>
       </c>
       <c r="R6" t="n">
-        <v>6511942</v>
+        <v>6511956</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119717409</v>
+        <v>119715785</v>
       </c>
       <c r="B7" t="n">
-        <v>91884</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,34 +1264,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Kvarnsjön, Kvarnsjön, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547484</v>
+        <v>547377</v>
       </c>
       <c r="R7" t="n">
-        <v>6512006</v>
+        <v>6511828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119715980</v>
+        <v>119716305</v>
       </c>
       <c r="B8" t="n">
         <v>94681</v>
@@ -1386,14 +1386,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547406</v>
+        <v>547559</v>
       </c>
       <c r="R8" t="n">
-        <v>6511874</v>
+        <v>6511883</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119714934</v>
+        <v>119715980</v>
       </c>
       <c r="B9" t="n">
         <v>94681</v>
@@ -1488,14 +1488,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547481</v>
+        <v>547406</v>
       </c>
       <c r="R9" t="n">
-        <v>6511713</v>
+        <v>6511874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119714119</v>
+        <v>119715947</v>
       </c>
       <c r="B10" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,38 +1566,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547512</v>
+        <v>547431</v>
       </c>
       <c r="R10" t="n">
-        <v>6511928</v>
+        <v>6511901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119716041</v>
+        <v>119715929</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,38 +1677,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547419</v>
+        <v>547424</v>
       </c>
       <c r="R11" t="n">
-        <v>6511911</v>
+        <v>6511875</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719483</v>
+        <v>119715352</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,21 +1792,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547493</v>
+        <v>547433</v>
       </c>
       <c r="R12" t="n">
-        <v>6511831</v>
+        <v>6511757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119719441</v>
+        <v>119714934</v>
       </c>
       <c r="B13" t="n">
-        <v>8432</v>
+        <v>94681</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,39 +1894,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547507</v>
+        <v>547481</v>
       </c>
       <c r="R13" t="n">
-        <v>6511795</v>
+        <v>6511713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119716007</v>
+        <v>119716041</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1992,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547408</v>
+        <v>547419</v>
       </c>
       <c r="R14" t="n">
-        <v>6511895</v>
+        <v>6511911</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119713893</v>
+        <v>119716135</v>
       </c>
       <c r="B15" t="n">
-        <v>91185</v>
+        <v>94681</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,21 +2098,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2109,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547450</v>
+        <v>547425</v>
       </c>
       <c r="R15" t="n">
-        <v>6511948</v>
+        <v>6511932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119716231</v>
+        <v>119715855</v>
       </c>
       <c r="B16" t="n">
-        <v>91884</v>
+        <v>91182</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,38 +2196,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547390</v>
+        <v>547401</v>
       </c>
       <c r="R16" t="n">
-        <v>6511934</v>
+        <v>6511820</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119715929</v>
+        <v>119719483</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2285,47 +2298,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547424</v>
+        <v>547493</v>
       </c>
       <c r="R17" t="n">
-        <v>6511875</v>
+        <v>6511831</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2384,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119715947</v>
+        <v>119719590</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,47 +2400,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547431</v>
+        <v>547449</v>
       </c>
       <c r="R18" t="n">
-        <v>6511901</v>
+        <v>6511879</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2490,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119714125</v>
+        <v>119719458</v>
       </c>
       <c r="B19" t="n">
-        <v>90966</v>
+        <v>91884</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,38 +2502,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5420</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547511</v>
+        <v>547493</v>
       </c>
       <c r="R19" t="n">
-        <v>6511918</v>
+        <v>6511831</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119713966</v>
+        <v>119716007</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2609,38 +2604,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547469</v>
+        <v>547408</v>
       </c>
       <c r="R20" t="n">
-        <v>6511781</v>
+        <v>6511895</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119715890</v>
+        <v>119719507</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2739,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547424</v>
+        <v>547463</v>
       </c>
       <c r="R21" t="n">
-        <v>6511854</v>
+        <v>6511851</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119715352</v>
+        <v>119714038</v>
       </c>
       <c r="B22" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2813,38 +2808,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547433</v>
+        <v>547465</v>
       </c>
       <c r="R22" t="n">
-        <v>6511757</v>
+        <v>6511856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119717214</v>
+        <v>119717409</v>
       </c>
       <c r="B23" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,25 +2910,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2943,10 +2938,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547509</v>
+        <v>547484</v>
       </c>
       <c r="R23" t="n">
-        <v>6511986</v>
+        <v>6512006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +3000,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119715785</v>
+        <v>119715959</v>
       </c>
       <c r="B24" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,38 +3012,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnsjön, Kvarnsjön, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547377</v>
+        <v>547424</v>
       </c>
       <c r="R24" t="n">
-        <v>6511828</v>
+        <v>6511904</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3107,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119719507</v>
+        <v>119719441</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>8432</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3119,38 +3123,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547463</v>
+        <v>547507</v>
       </c>
       <c r="R25" t="n">
-        <v>6511851</v>
+        <v>6511795</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119714038</v>
+        <v>119713966</v>
       </c>
       <c r="B26" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3221,38 +3230,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547465</v>
+        <v>547469</v>
       </c>
       <c r="R26" t="n">
-        <v>6511856</v>
+        <v>6511781</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119715959</v>
+        <v>119713893</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3323,47 +3332,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547424</v>
+        <v>547450</v>
       </c>
       <c r="R27" t="n">
-        <v>6511904</v>
+        <v>6511948</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119715855</v>
+        <v>119715890</v>
       </c>
       <c r="B28" t="n">
-        <v>91182</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3434,38 +3434,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547401</v>
+        <v>547424</v>
       </c>
       <c r="R28" t="n">
-        <v>6511820</v>
+        <v>6511854</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119716241</v>
+        <v>119714125</v>
       </c>
       <c r="B29" t="n">
-        <v>90527</v>
+        <v>90966</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>5420</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547391</v>
+        <v>547511</v>
       </c>
       <c r="R29" t="n">
-        <v>6511960</v>
+        <v>6511918</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119716135</v>
+        <v>119717214</v>
       </c>
       <c r="B30" t="n">
         <v>94681</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547425</v>
+        <v>547509</v>
       </c>
       <c r="R30" t="n">
-        <v>6511932</v>
+        <v>6511986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119719458</v>
+        <v>119716241</v>
       </c>
       <c r="B31" t="n">
-        <v>91884</v>
+        <v>90527</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3740,38 +3740,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547493</v>
+        <v>547391</v>
       </c>
       <c r="R31" t="n">
-        <v>6511831</v>
+        <v>6511960</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119716305</v>
+        <v>119716231</v>
       </c>
       <c r="B32" t="n">
-        <v>94681</v>
+        <v>91884</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3842,38 +3842,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547559</v>
+        <v>547390</v>
       </c>
       <c r="R32" t="n">
-        <v>6511883</v>
+        <v>6511934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119719590</v>
+        <v>119714119</v>
       </c>
       <c r="B33" t="n">
         <v>91185</v>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547449</v>
+        <v>547512</v>
       </c>
       <c r="R33" t="n">
-        <v>6511879</v>
+        <v>6511928</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120116586</v>
+        <v>120116625</v>
       </c>
       <c r="B36" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,25 +4299,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4327,24 +4327,29 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åfallet SV 430 m, Ög</t>
+          <t>Åfallet SV 418 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547434</v>
+        <v>547469</v>
       </c>
       <c r="R36" t="n">
-        <v>6511887</v>
+        <v>6511866</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4374,6 +4379,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4406,10 +4416,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120116625</v>
+        <v>120116586</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4418,25 +4428,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4446,29 +4456,24 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åfallet SV 418 m, Ög</t>
+          <t>Åfallet SV 430 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547469</v>
+        <v>547434</v>
       </c>
       <c r="R37" t="n">
-        <v>6511866</v>
+        <v>6511887</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4498,11 +4503,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -2898,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119717409</v>
+        <v>119715959</v>
       </c>
       <c r="B23" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,38 +2910,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547484</v>
+        <v>547424</v>
       </c>
       <c r="R23" t="n">
-        <v>6512006</v>
+        <v>6511904</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3000,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119715959</v>
+        <v>119717409</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,47 +3021,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547424</v>
+        <v>547484</v>
       </c>
       <c r="R24" t="n">
-        <v>6511904</v>
+        <v>6512006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -2898,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119715959</v>
+        <v>119717409</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,47 +2910,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547424</v>
+        <v>547484</v>
       </c>
       <c r="R23" t="n">
-        <v>6511904</v>
+        <v>6512006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3000,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119717409</v>
+        <v>119715959</v>
       </c>
       <c r="B24" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,38 +3012,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547484</v>
+        <v>547424</v>
       </c>
       <c r="R24" t="n">
-        <v>6512006</v>
+        <v>6511904</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119715785</v>
+        <v>119714119</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>91203</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1260,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarnsjön, Kvarnsjön, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547377</v>
+        <v>547512</v>
       </c>
       <c r="R7" t="n">
-        <v>6511828</v>
+        <v>6511928</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119716305</v>
+        <v>119713893</v>
       </c>
       <c r="B8" t="n">
-        <v>94681</v>
+        <v>91203</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,34 +1366,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547559</v>
+        <v>547450</v>
       </c>
       <c r="R8" t="n">
-        <v>6511883</v>
+        <v>6511948</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119715980</v>
+        <v>119715890</v>
       </c>
       <c r="B9" t="n">
-        <v>94681</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547406</v>
+        <v>547424</v>
       </c>
       <c r="R9" t="n">
-        <v>6511874</v>
+        <v>6511854</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119715947</v>
+        <v>119715352</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>94704</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,47 +1566,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547431</v>
+        <v>547433</v>
       </c>
       <c r="R10" t="n">
-        <v>6511901</v>
+        <v>6511757</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119715929</v>
+        <v>119716305</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>94704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,47 +1668,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547424</v>
+        <v>547559</v>
       </c>
       <c r="R11" t="n">
-        <v>6511875</v>
+        <v>6511883</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119715352</v>
+        <v>119714934</v>
       </c>
       <c r="B12" t="n">
-        <v>94681</v>
+        <v>94704</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547433</v>
+        <v>547481</v>
       </c>
       <c r="R12" t="n">
-        <v>6511757</v>
+        <v>6511713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119714934</v>
+        <v>119714125</v>
       </c>
       <c r="B13" t="n">
-        <v>94681</v>
+        <v>90984</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,34 +1876,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547481</v>
+        <v>547511</v>
       </c>
       <c r="R13" t="n">
-        <v>6511713</v>
+        <v>6511918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119716041</v>
+        <v>119717409</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,25 +1974,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2020,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547419</v>
+        <v>547484</v>
       </c>
       <c r="R14" t="n">
-        <v>6511911</v>
+        <v>6512006</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119716135</v>
+        <v>119715959</v>
       </c>
       <c r="B15" t="n">
-        <v>94681</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,38 +2076,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547425</v>
+        <v>547424</v>
       </c>
       <c r="R15" t="n">
-        <v>6511932</v>
+        <v>6511904</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119715855</v>
+        <v>119716041</v>
       </c>
       <c r="B16" t="n">
-        <v>91182</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,34 +2191,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>547401</v>
+        <v>547419</v>
       </c>
       <c r="R16" t="n">
-        <v>6511820</v>
+        <v>6511911</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119719483</v>
+        <v>119715929</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,38 +2289,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>547493</v>
+        <v>547424</v>
       </c>
       <c r="R17" t="n">
-        <v>6511831</v>
+        <v>6511875</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119719590</v>
+        <v>119717214</v>
       </c>
       <c r="B18" t="n">
-        <v>91185</v>
+        <v>94704</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,21 +2404,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>547449</v>
+        <v>547509</v>
       </c>
       <c r="R18" t="n">
-        <v>6511879</v>
+        <v>6511986</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,10 +2490,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119719458</v>
+        <v>119714038</v>
       </c>
       <c r="B19" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,14 +2526,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>547493</v>
+        <v>547465</v>
       </c>
       <c r="R19" t="n">
-        <v>6511831</v>
+        <v>6511856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119716007</v>
+        <v>119719483</v>
       </c>
       <c r="B20" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,38 +2604,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>547408</v>
+        <v>547493</v>
       </c>
       <c r="R20" t="n">
-        <v>6511895</v>
+        <v>6511831</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119719507</v>
+        <v>119715785</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,34 +2710,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Kvarnsjön, Kvarnsjön, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>547463</v>
+        <v>547377</v>
       </c>
       <c r="R21" t="n">
-        <v>6511851</v>
+        <v>6511828</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119714038</v>
+        <v>119716007</v>
       </c>
       <c r="B22" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>547465</v>
+        <v>547408</v>
       </c>
       <c r="R22" t="n">
-        <v>6511856</v>
+        <v>6511895</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,10 +2898,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119717409</v>
+        <v>119719590</v>
       </c>
       <c r="B23" t="n">
-        <v>91884</v>
+        <v>91203</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,25 +2910,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>6031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>547484</v>
+        <v>547449</v>
       </c>
       <c r="R23" t="n">
-        <v>6512006</v>
+        <v>6511879</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3000,10 +3000,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119715959</v>
+        <v>119719441</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,47 +3012,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>547424</v>
+        <v>547507</v>
       </c>
       <c r="R24" t="n">
-        <v>6511904</v>
+        <v>6511795</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3107,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119719441</v>
+        <v>119715947</v>
       </c>
       <c r="B25" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,43 +3119,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>547507</v>
+        <v>547431</v>
       </c>
       <c r="R25" t="n">
-        <v>6511795</v>
+        <v>6511901</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119713966</v>
+        <v>119716241</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,34 +3234,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lotorpsån, Lotorpsån, Ög</t>
+          <t>Åfallet, Åfallet, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>547469</v>
+        <v>547391</v>
       </c>
       <c r="R26" t="n">
-        <v>6511781</v>
+        <v>6511960</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119713893</v>
+        <v>119719507</v>
       </c>
       <c r="B27" t="n">
-        <v>91185</v>
+        <v>91902</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3332,25 +3332,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547450</v>
+        <v>547463</v>
       </c>
       <c r="R27" t="n">
-        <v>6511948</v>
+        <v>6511851</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119715890</v>
+        <v>119713966</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3434,38 +3434,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547424</v>
+        <v>547469</v>
       </c>
       <c r="R28" t="n">
-        <v>6511854</v>
+        <v>6511781</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119714125</v>
+        <v>119719458</v>
       </c>
       <c r="B29" t="n">
-        <v>90966</v>
+        <v>91902</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3536,38 +3536,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5420</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547511</v>
+        <v>547493</v>
       </c>
       <c r="R29" t="n">
-        <v>6511918</v>
+        <v>6511831</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119717214</v>
+        <v>119716231</v>
       </c>
       <c r="B30" t="n">
-        <v>94681</v>
+        <v>91902</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3638,25 +3638,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547509</v>
+        <v>547390</v>
       </c>
       <c r="R30" t="n">
-        <v>6511986</v>
+        <v>6511934</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119716241</v>
+        <v>119716135</v>
       </c>
       <c r="B31" t="n">
-        <v>90527</v>
+        <v>94704</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>547391</v>
+        <v>547425</v>
       </c>
       <c r="R31" t="n">
-        <v>6511960</v>
+        <v>6511932</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119716231</v>
+        <v>119715855</v>
       </c>
       <c r="B32" t="n">
-        <v>91884</v>
+        <v>91200</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3842,38 +3842,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>1339</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åfallet, Åfallet, Ög</t>
+          <t>Lotorpsån, Lotorpsån, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547390</v>
+        <v>547401</v>
       </c>
       <c r="R32" t="n">
-        <v>6511934</v>
+        <v>6511820</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119714119</v>
+        <v>119715980</v>
       </c>
       <c r="B33" t="n">
-        <v>91185</v>
+        <v>94704</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3948,21 +3948,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547512</v>
+        <v>547406</v>
       </c>
       <c r="R33" t="n">
-        <v>6511928</v>
+        <v>6511874</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4034,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120116608</v>
+        <v>120116625</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4086,14 +4086,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åfallet SV 420 m, Ög</t>
+          <t>Åfallet SV 418 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547447</v>
+        <v>547469</v>
       </c>
       <c r="R34" t="n">
-        <v>6511886</v>
+        <v>6511866</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4126,6 +4126,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4158,10 +4163,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120116681</v>
+        <v>120116608</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4193,7 +4198,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4210,14 +4215,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åfallet SV 435 m, Ög</t>
+          <t>Åfallet SV 420 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547456</v>
+        <v>547447</v>
       </c>
       <c r="R35" t="n">
-        <v>6511852</v>
+        <v>6511886</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4250,11 +4255,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4287,10 +4287,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120116625</v>
+        <v>120116586</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>91203</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,25 +4299,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4327,29 +4327,24 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åfallet SV 418 m, Ög</t>
+          <t>Åfallet SV 430 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547469</v>
+        <v>547434</v>
       </c>
       <c r="R36" t="n">
-        <v>6511866</v>
+        <v>6511887</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4379,11 +4374,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4416,10 +4406,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120116586</v>
+        <v>120116681</v>
       </c>
       <c r="B37" t="n">
-        <v>91185</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4428,52 +4418,57 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åfallet SV 430 m, Ög</t>
+          <t>Åfallet SV 435 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547434</v>
+        <v>547456</v>
       </c>
       <c r="R37" t="n">
-        <v>6511887</v>
+        <v>6511852</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4503,6 +4498,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4538,7 +4538,7 @@
         <v>120116696</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4034,7 +4034,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120116625</v>
+        <v>120116681</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4086,14 +4086,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åfallet SV 418 m, Ög</t>
+          <t>Åfallet SV 435 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547469</v>
+        <v>547456</v>
       </c>
       <c r="R34" t="n">
-        <v>6511866</v>
+        <v>6511852</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4163,10 +4163,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120116608</v>
+        <v>120116586</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,57 +4175,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åfallet SV 420 m, Ög</t>
+          <t>Åfallet SV 430 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547447</v>
+        <v>547434</v>
       </c>
       <c r="R35" t="n">
-        <v>6511886</v>
+        <v>6511887</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4287,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120116586</v>
+        <v>120116696</v>
       </c>
       <c r="B36" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,52 +4294,57 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åfallet SV 430 m, Ög</t>
+          <t>Åfallet SV 425 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547434</v>
+        <v>547490</v>
       </c>
       <c r="R36" t="n">
-        <v>6511887</v>
+        <v>6511838</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4374,6 +4374,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4406,7 +4411,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120116681</v>
+        <v>120116608</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4441,7 +4446,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4458,14 +4463,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åfallet SV 435 m, Ög</t>
+          <t>Åfallet SV 420 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547456</v>
+        <v>547447</v>
       </c>
       <c r="R37" t="n">
-        <v>6511852</v>
+        <v>6511886</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4498,11 +4503,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4535,7 +4535,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120116696</v>
+        <v>120116625</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4587,14 +4587,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åfallet SV 425 m, Ög</t>
+          <t>Åfallet SV 418 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547490</v>
+        <v>547469</v>
       </c>
       <c r="R38" t="n">
-        <v>6511838</v>
+        <v>6511866</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4034,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120116681</v>
+        <v>120116586</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,57 +4046,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åfallet SV 435 m, Ög</t>
+          <t>Åfallet SV 430 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547456</v>
+        <v>547434</v>
       </c>
       <c r="R34" t="n">
-        <v>6511852</v>
+        <v>6511887</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4126,11 +4121,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4163,10 +4153,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120116586</v>
+        <v>120116696</v>
       </c>
       <c r="B35" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,52 +4165,57 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åfallet SV 430 m, Ög</t>
+          <t>Åfallet SV 425 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547434</v>
+        <v>547490</v>
       </c>
       <c r="R35" t="n">
-        <v>6511887</v>
+        <v>6511838</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4250,6 +4245,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120116696</v>
+        <v>120116681</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4334,14 +4334,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åfallet SV 425 m, Ög</t>
+          <t>Åfallet SV 435 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547490</v>
+        <v>547456</v>
       </c>
       <c r="R36" t="n">
-        <v>6511838</v>
+        <v>6511852</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4411,7 +4411,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120116608</v>
+        <v>120116625</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4463,14 +4463,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åfallet SV 420 m, Ög</t>
+          <t>Åfallet SV 418 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547447</v>
+        <v>547469</v>
       </c>
       <c r="R37" t="n">
-        <v>6511886</v>
+        <v>6511866</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,6 +4503,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4535,7 +4540,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120116625</v>
+        <v>120116608</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4570,7 +4575,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4587,14 +4592,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åfallet SV 418 m, Ög</t>
+          <t>Åfallet SV 420 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547469</v>
+        <v>547447</v>
       </c>
       <c r="R38" t="n">
-        <v>6511866</v>
+        <v>6511886</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4627,11 +4632,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4034,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120116586</v>
+        <v>120116696</v>
       </c>
       <c r="B34" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,52 +4046,57 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åfallet SV 430 m, Ög</t>
+          <t>Åfallet SV 425 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547434</v>
+        <v>547490</v>
       </c>
       <c r="R34" t="n">
-        <v>6511887</v>
+        <v>6511838</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4121,6 +4126,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4153,10 +4163,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120116696</v>
+        <v>120116586</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4165,57 +4175,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åfallet SV 425 m, Ög</t>
+          <t>Åfallet SV 430 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547490</v>
+        <v>547434</v>
       </c>
       <c r="R35" t="n">
-        <v>6511838</v>
+        <v>6511887</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4245,11 +4250,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120116681</v>
+        <v>120116608</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4334,14 +4334,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åfallet SV 435 m, Ög</t>
+          <t>Åfallet SV 420 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547456</v>
+        <v>547447</v>
       </c>
       <c r="R36" t="n">
-        <v>6511852</v>
+        <v>6511886</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,11 +4374,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4411,7 +4406,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120116625</v>
+        <v>120116681</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4446,7 +4441,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4463,14 +4458,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åfallet SV 418 m, Ög</t>
+          <t>Åfallet SV 435 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547469</v>
+        <v>547456</v>
       </c>
       <c r="R37" t="n">
-        <v>6511866</v>
+        <v>6511852</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4507,7 +4502,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4540,7 +4535,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120116608</v>
+        <v>120116625</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4575,7 +4570,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4592,14 +4587,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åfallet SV 420 m, Ög</t>
+          <t>Åfallet SV 418 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547447</v>
+        <v>547469</v>
       </c>
       <c r="R38" t="n">
-        <v>6511886</v>
+        <v>6511866</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4632,6 +4627,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4034,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120116696</v>
+        <v>120116586</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,57 +4046,52 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åfallet SV 425 m, Ög</t>
+          <t>Åfallet SV 430 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547490</v>
+        <v>547434</v>
       </c>
       <c r="R34" t="n">
-        <v>6511838</v>
+        <v>6511887</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4126,11 +4121,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4163,10 +4153,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120116586</v>
+        <v>120116696</v>
       </c>
       <c r="B35" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,52 +4165,57 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åfallet SV 430 m, Ög</t>
+          <t>Åfallet SV 425 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547434</v>
+        <v>547490</v>
       </c>
       <c r="R35" t="n">
-        <v>6511887</v>
+        <v>6511838</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4250,6 +4245,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4406,7 +4406,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120116681</v>
+        <v>120116625</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4458,14 +4458,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åfallet SV 435 m, Ög</t>
+          <t>Åfallet SV 418 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547456</v>
+        <v>547469</v>
       </c>
       <c r="R37" t="n">
-        <v>6511852</v>
+        <v>6511866</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4535,7 +4535,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120116625</v>
+        <v>120116681</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4587,14 +4587,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åfallet SV 418 m, Ög</t>
+          <t>Åfallet SV 435 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547469</v>
+        <v>547456</v>
       </c>
       <c r="R38" t="n">
-        <v>6511866</v>
+        <v>6511852</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4034,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120116586</v>
+        <v>120116625</v>
       </c>
       <c r="B34" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,25 +4046,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4074,24 +4074,29 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åfallet SV 430 m, Ög</t>
+          <t>Åfallet SV 418 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547434</v>
+        <v>547469</v>
       </c>
       <c r="R34" t="n">
-        <v>6511887</v>
+        <v>6511866</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4121,6 +4126,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4153,10 +4163,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120116696</v>
+        <v>120116586</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4165,57 +4175,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åfallet SV 425 m, Ög</t>
+          <t>Åfallet SV 430 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547490</v>
+        <v>547434</v>
       </c>
       <c r="R35" t="n">
-        <v>6511838</v>
+        <v>6511887</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4245,11 +4250,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,7 +4282,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120116608</v>
+        <v>120116696</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4334,14 +4334,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åfallet SV 420 m, Ög</t>
+          <t>Åfallet SV 425 m, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>547447</v>
+        <v>547490</v>
       </c>
       <c r="R36" t="n">
-        <v>6511886</v>
+        <v>6511838</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4374,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fyndplatsen ligger 2 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4406,7 +4411,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120116625</v>
+        <v>120116681</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4441,7 +4446,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4458,14 +4463,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åfallet SV 418 m, Ög</t>
+          <t>Åfallet SV 435 m, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>547469</v>
+        <v>547456</v>
       </c>
       <c r="R37" t="n">
-        <v>6511866</v>
+        <v>6511852</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,7 +4507,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4535,7 +4540,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120116681</v>
+        <v>120116608</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4570,7 +4575,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4587,14 +4592,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åfallet SV 435 m, Ög</t>
+          <t>Åfallet SV 420 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547456</v>
+        <v>547447</v>
       </c>
       <c r="R38" t="n">
-        <v>6511852</v>
+        <v>6511886</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4627,11 +4632,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 12 meter från fällda träd och 5 meter från underröjda träd.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4034,7 +4034,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120116625</v>
+        <v>120116608</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4086,14 +4086,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åfallet SV 418 m, Ög</t>
+          <t>Åfallet SV 420 m, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547469</v>
+        <v>547447</v>
       </c>
       <c r="R34" t="n">
-        <v>6511866</v>
+        <v>6511886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4126,11 +4126,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4163,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120116586</v>
+        <v>120116625</v>
       </c>
       <c r="B35" t="n">
-        <v>91203</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,25 +4170,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4203,24 +4198,29 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åfallet SV 430 m, Ög</t>
+          <t>Åfallet SV 418 m, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>547434</v>
+        <v>547469</v>
       </c>
       <c r="R35" t="n">
-        <v>6511887</v>
+        <v>6511866</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4250,6 +4250,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Har ej letat efter knärot under riset från skogsavverkningen. Fyndplatsen ligger 3 meter från hyggeskanten.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4540,10 +4545,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120116608</v>
+        <v>120116586</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>91203</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4552,57 +4557,52 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åfallet SV 420 m, Ög</t>
+          <t>Åfallet SV 430 m, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>547447</v>
+        <v>547434</v>
       </c>
       <c r="R38" t="n">
-        <v>6511886</v>
+        <v>6511887</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4667,7 +4667,7 @@
         <v>121264581</v>
       </c>
       <c r="B39" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4667,7 +4667,7 @@
         <v>121264581</v>
       </c>
       <c r="B39" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4667,7 +4667,7 @@
         <v>121264581</v>
       </c>
       <c r="B39" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4667,7 +4667,7 @@
         <v>121264581</v>
       </c>
       <c r="B39" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4667,7 +4667,7 @@
         <v>121264581</v>
       </c>
       <c r="B39" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4667,7 +4667,7 @@
         <v>121264581</v>
       </c>
       <c r="B39" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4791,6 +4791,3350 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122748078</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tretjärnarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>547386</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6511902</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122748081</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tretjärnarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>547401</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6511938</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122748100</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nordatbodarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>547368</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6511855</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122748111</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91460</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nordatbodarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>547434</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6511758</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122748090</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tretjärnarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>547445</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6511922</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122748109</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Högbrånan NÖ, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>547448</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6511787</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122748124</v>
+      </c>
+      <c r="B46" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Renskinns- V, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>547381</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6511990</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122748030</v>
+      </c>
+      <c r="B47" t="n">
+        <v>90837</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ängeskälen NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>547653</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6511677</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På tallåga som hänger mot lodyta</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122748101</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Nordatbodarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>547370</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6511844</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122748102</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Nordatbodarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>547378</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6511826</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122748123</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91460</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Renskinns- V, Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>547401</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6511980</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122748072</v>
+      </c>
+      <c r="B51" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hocklet N, Ög</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>547386</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6511963</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122747992</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92146</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Buberget V, Ög</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>547401</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6511893</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Väster om stigen</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122748077</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79278</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tretjärnarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>547364</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6511915</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122748122</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92146</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lerbäcken V, Ög</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>547410</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6511972</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122748068</v>
+      </c>
+      <c r="B55" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hocklet N, Ög</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>547411</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6511968</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122748103</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Högbrånan Ö, Ög</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>547389</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6511805</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122748009</v>
+      </c>
+      <c r="B57" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hocklet N, Ög</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>547564</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6511874</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122748097</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Salaligan N, Ög</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>547426</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6511886</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122748001</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91059</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Buberget V, Ög</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>547501</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6511967</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122748070</v>
+      </c>
+      <c r="B60" t="n">
+        <v>90802</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hocklet N, Ög</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>547388</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6511959</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122748110</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92118</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Nordatbodarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>547424</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6511755</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122748098</v>
+      </c>
+      <c r="B62" t="n">
+        <v>105350</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Salaligan N, Ög</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>547433</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6511877</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122748106</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Salaligan N, Ög</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>547396</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6511793</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122748005</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Källan N, Ög</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>547535</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6511922</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122748079</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92144</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Tretjärnarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>547387</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6511907</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122748006</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91247</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hocklet N, Ög</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>547516</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6511927</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>122748002</v>
+      </c>
+      <c r="B67" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Källan N, Ög</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>547505</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6511966</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122748007</v>
+      </c>
+      <c r="B68" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hocklet N, Ög</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>547554</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6511871</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122748033</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92153</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Buberget NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>547612</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6511812</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122748095</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91247</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden V, Ög</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>547464</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6511904</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748078</v>
+        <v>122748077</v>
       </c>
       <c r="B40" t="n">
-        <v>92153</v>
+        <v>79380</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4809,21 +4809,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547386</v>
+        <v>547364</v>
       </c>
       <c r="R40" t="n">
-        <v>6511902</v>
+        <v>6511915</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748081</v>
+        <v>122747992</v>
       </c>
       <c r="B41" t="n">
-        <v>92153</v>
+        <v>92249</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,34 +4915,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>547401</v>
       </c>
       <c r="R41" t="n">
-        <v>6511938</v>
+        <v>6511893</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4975,6 +4975,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748100</v>
+        <v>122748090</v>
       </c>
       <c r="B42" t="n">
-        <v>5173</v>
+        <v>92256</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,38 +5022,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547368</v>
+        <v>547445</v>
       </c>
       <c r="R42" t="n">
-        <v>6511855</v>
+        <v>6511922</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5111,10 +5116,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748111</v>
+        <v>122748078</v>
       </c>
       <c r="B43" t="n">
-        <v>91460</v>
+        <v>92256</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5123,38 +5128,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547434</v>
+        <v>547386</v>
       </c>
       <c r="R43" t="n">
-        <v>6511758</v>
+        <v>6511902</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5217,10 +5222,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748090</v>
+        <v>122748124</v>
       </c>
       <c r="B44" t="n">
-        <v>92153</v>
+        <v>95118</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5229,38 +5234,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547445</v>
+        <v>547381</v>
       </c>
       <c r="R44" t="n">
-        <v>6511922</v>
+        <v>6511990</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,6 +5298,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5323,10 +5333,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748109</v>
+        <v>122748079</v>
       </c>
       <c r="B45" t="n">
-        <v>92153</v>
+        <v>92247</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5339,34 +5349,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547448</v>
+        <v>547387</v>
       </c>
       <c r="R45" t="n">
-        <v>6511787</v>
+        <v>6511907</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5429,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748124</v>
+        <v>122748007</v>
       </c>
       <c r="B46" t="n">
-        <v>95015</v>
+        <v>95118</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5465,14 +5475,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547381</v>
+        <v>547554</v>
       </c>
       <c r="R46" t="n">
-        <v>6511990</v>
+        <v>6511871</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,11 +5515,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5540,10 +5545,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748030</v>
+        <v>122748102</v>
       </c>
       <c r="B47" t="n">
-        <v>90837</v>
+        <v>92256</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5556,34 +5561,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547653</v>
+        <v>547378</v>
       </c>
       <c r="R47" t="n">
-        <v>6511677</v>
+        <v>6511826</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5616,11 +5621,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5651,10 +5651,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748101</v>
+        <v>122748103</v>
       </c>
       <c r="B48" t="n">
-        <v>5173</v>
+        <v>98347</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5663,38 +5663,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547370</v>
+        <v>547389</v>
       </c>
       <c r="R48" t="n">
-        <v>6511844</v>
+        <v>6511805</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,6 +5736,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5757,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748102</v>
+        <v>122748095</v>
       </c>
       <c r="B49" t="n">
-        <v>92153</v>
+        <v>91350</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5769,38 +5783,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547378</v>
+        <v>547464</v>
       </c>
       <c r="R49" t="n">
-        <v>6511826</v>
+        <v>6511904</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5863,10 +5877,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748123</v>
+        <v>122748101</v>
       </c>
       <c r="B50" t="n">
-        <v>91460</v>
+        <v>5173</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5879,34 +5893,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6031</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547401</v>
+        <v>547370</v>
       </c>
       <c r="R50" t="n">
-        <v>6511980</v>
+        <v>6511844</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5969,10 +5983,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748072</v>
+        <v>122748109</v>
       </c>
       <c r="B51" t="n">
-        <v>95015</v>
+        <v>92256</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5981,38 +5995,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547386</v>
+        <v>547448</v>
       </c>
       <c r="R51" t="n">
-        <v>6511963</v>
+        <v>6511787</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6045,11 +6059,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6080,10 +6089,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122747992</v>
+        <v>122748122</v>
       </c>
       <c r="B52" t="n">
-        <v>92146</v>
+        <v>92249</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,14 +6125,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547401</v>
+        <v>547410</v>
       </c>
       <c r="R52" t="n">
-        <v>6511893</v>
+        <v>6511972</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6156,11 +6165,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6191,10 +6195,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748077</v>
+        <v>122748081</v>
       </c>
       <c r="B53" t="n">
-        <v>79278</v>
+        <v>92256</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6207,21 +6211,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6231,10 +6235,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547364</v>
+        <v>547401</v>
       </c>
       <c r="R53" t="n">
-        <v>6511915</v>
+        <v>6511938</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6297,10 +6301,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748122</v>
+        <v>122748030</v>
       </c>
       <c r="B54" t="n">
-        <v>92146</v>
+        <v>90940</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6313,34 +6317,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547410</v>
+        <v>547653</v>
       </c>
       <c r="R54" t="n">
-        <v>6511972</v>
+        <v>6511677</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6373,6 +6377,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6403,10 +6412,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748068</v>
+        <v>122748033</v>
       </c>
       <c r="B55" t="n">
-        <v>95015</v>
+        <v>92256</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6415,38 +6424,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547411</v>
+        <v>547612</v>
       </c>
       <c r="R55" t="n">
-        <v>6511968</v>
+        <v>6511812</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6479,11 +6488,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6514,10 +6518,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748103</v>
+        <v>122748100</v>
       </c>
       <c r="B56" t="n">
-        <v>98244</v>
+        <v>5173</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6526,47 +6530,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547389</v>
+        <v>547368</v>
       </c>
       <c r="R56" t="n">
-        <v>6511805</v>
+        <v>6511855</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,11 +6594,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6634,10 +6624,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748009</v>
+        <v>122748001</v>
       </c>
       <c r="B57" t="n">
-        <v>95015</v>
+        <v>91162</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6646,38 +6636,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547564</v>
+        <v>547501</v>
       </c>
       <c r="R57" t="n">
-        <v>6511874</v>
+        <v>6511967</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6740,10 +6730,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748097</v>
+        <v>122748070</v>
       </c>
       <c r="B58" t="n">
-        <v>98244</v>
+        <v>90905</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6752,47 +6742,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547426</v>
+        <v>547388</v>
       </c>
       <c r="R58" t="n">
-        <v>6511886</v>
+        <v>6511959</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6825,11 +6806,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6860,10 +6836,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748001</v>
+        <v>122748098</v>
       </c>
       <c r="B59" t="n">
-        <v>91059</v>
+        <v>105453</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6872,38 +6848,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1101</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547501</v>
+        <v>547433</v>
       </c>
       <c r="R59" t="n">
-        <v>6511967</v>
+        <v>6511877</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6966,10 +6942,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748070</v>
+        <v>122748006</v>
       </c>
       <c r="B60" t="n">
-        <v>90802</v>
+        <v>91350</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6982,21 +6958,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>5420</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7006,10 +6982,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547388</v>
+        <v>547516</v>
       </c>
       <c r="R60" t="n">
-        <v>6511959</v>
+        <v>6511927</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7075,7 +7051,7 @@
         <v>122748110</v>
       </c>
       <c r="B61" t="n">
-        <v>92118</v>
+        <v>92221</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7178,10 +7154,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748098</v>
+        <v>122748106</v>
       </c>
       <c r="B62" t="n">
-        <v>105350</v>
+        <v>92256</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7190,25 +7166,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7218,10 +7194,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547433</v>
+        <v>547396</v>
       </c>
       <c r="R62" t="n">
-        <v>6511877</v>
+        <v>6511793</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7284,10 +7260,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748106</v>
+        <v>122748097</v>
       </c>
       <c r="B63" t="n">
-        <v>92153</v>
+        <v>98347</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7296,38 +7272,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547396</v>
+        <v>547426</v>
       </c>
       <c r="R63" t="n">
-        <v>6511793</v>
+        <v>6511886</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7360,6 +7345,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7390,10 +7380,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748005</v>
+        <v>122748072</v>
       </c>
       <c r="B64" t="n">
-        <v>92153</v>
+        <v>95118</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7402,38 +7392,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547535</v>
+        <v>547386</v>
       </c>
       <c r="R64" t="n">
-        <v>6511922</v>
+        <v>6511963</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7466,6 +7456,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7496,10 +7491,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748079</v>
+        <v>122748123</v>
       </c>
       <c r="B65" t="n">
-        <v>92144</v>
+        <v>91563</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7508,38 +7503,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5448</v>
+        <v>6031</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547387</v>
+        <v>547401</v>
       </c>
       <c r="R65" t="n">
-        <v>6511907</v>
+        <v>6511980</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7602,10 +7597,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748006</v>
+        <v>122748111</v>
       </c>
       <c r="B66" t="n">
-        <v>91247</v>
+        <v>91563</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7618,34 +7613,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5420</v>
+        <v>6031</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547516</v>
+        <v>547434</v>
       </c>
       <c r="R66" t="n">
-        <v>6511927</v>
+        <v>6511758</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7708,10 +7703,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748002</v>
+        <v>122748068</v>
       </c>
       <c r="B67" t="n">
-        <v>95015</v>
+        <v>95118</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7744,14 +7739,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547505</v>
+        <v>547411</v>
       </c>
       <c r="R67" t="n">
-        <v>6511966</v>
+        <v>6511968</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7788,7 +7783,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt längs stigen</t>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7819,10 +7814,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748007</v>
+        <v>122748009</v>
       </c>
       <c r="B68" t="n">
-        <v>95015</v>
+        <v>95118</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7859,10 +7854,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547554</v>
+        <v>547564</v>
       </c>
       <c r="R68" t="n">
-        <v>6511871</v>
+        <v>6511874</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7925,10 +7920,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748033</v>
+        <v>122748002</v>
       </c>
       <c r="B69" t="n">
-        <v>92153</v>
+        <v>95118</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7937,38 +7932,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547612</v>
+        <v>547505</v>
       </c>
       <c r="R69" t="n">
-        <v>6511812</v>
+        <v>6511966</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8001,6 +7996,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8031,10 +8031,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748095</v>
+        <v>122748005</v>
       </c>
       <c r="B70" t="n">
-        <v>91247</v>
+        <v>92256</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8043,38 +8043,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547464</v>
+        <v>547535</v>
       </c>
       <c r="R70" t="n">
-        <v>6511904</v>
+        <v>6511922</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -6942,10 +6942,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748006</v>
+        <v>122748110</v>
       </c>
       <c r="B60" t="n">
-        <v>91350</v>
+        <v>92221</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6958,34 +6958,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547516</v>
+        <v>547424</v>
       </c>
       <c r="R60" t="n">
-        <v>6511927</v>
+        <v>6511755</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,10 +7048,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748110</v>
+        <v>122748006</v>
       </c>
       <c r="B61" t="n">
-        <v>92221</v>
+        <v>91350</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7064,34 +7064,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547424</v>
+        <v>547516</v>
       </c>
       <c r="R61" t="n">
-        <v>6511755</v>
+        <v>6511927</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748077</v>
+        <v>122748009</v>
       </c>
       <c r="B40" t="n">
-        <v>79380</v>
+        <v>95126</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4805,38 +4805,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547364</v>
+        <v>547564</v>
       </c>
       <c r="R40" t="n">
-        <v>6511915</v>
+        <v>6511874</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122747992</v>
+        <v>122748068</v>
       </c>
       <c r="B41" t="n">
-        <v>92249</v>
+        <v>95126</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4911,38 +4911,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547401</v>
+        <v>547411</v>
       </c>
       <c r="R41" t="n">
-        <v>6511893</v>
+        <v>6511968</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Väster om stigen</t>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748090</v>
+        <v>122748103</v>
       </c>
       <c r="B42" t="n">
-        <v>92256</v>
+        <v>98355</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5022,38 +5022,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547445</v>
+        <v>547389</v>
       </c>
       <c r="R42" t="n">
-        <v>6511922</v>
+        <v>6511805</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5086,6 +5095,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5116,10 +5130,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748078</v>
+        <v>122748101</v>
       </c>
       <c r="B43" t="n">
-        <v>92256</v>
+        <v>5173</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5128,38 +5142,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547386</v>
+        <v>547370</v>
       </c>
       <c r="R43" t="n">
-        <v>6511902</v>
+        <v>6511844</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5222,10 +5236,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748124</v>
+        <v>122748095</v>
       </c>
       <c r="B44" t="n">
-        <v>95118</v>
+        <v>91354</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5238,34 +5252,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547381</v>
+        <v>547464</v>
       </c>
       <c r="R44" t="n">
-        <v>6511990</v>
+        <v>6511904</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5298,11 +5312,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748079</v>
+        <v>122748070</v>
       </c>
       <c r="B45" t="n">
-        <v>92247</v>
+        <v>90909</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5345,38 +5354,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547387</v>
+        <v>547388</v>
       </c>
       <c r="R45" t="n">
-        <v>6511907</v>
+        <v>6511959</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5439,10 +5448,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748007</v>
+        <v>122748030</v>
       </c>
       <c r="B46" t="n">
-        <v>95118</v>
+        <v>90944</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5451,38 +5460,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547554</v>
+        <v>547653</v>
       </c>
       <c r="R46" t="n">
-        <v>6511871</v>
+        <v>6511677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,6 +5524,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5545,10 +5559,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748102</v>
+        <v>122748110</v>
       </c>
       <c r="B47" t="n">
-        <v>92256</v>
+        <v>92225</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5557,25 +5571,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5599,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547378</v>
+        <v>547424</v>
       </c>
       <c r="R47" t="n">
-        <v>6511826</v>
+        <v>6511755</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5651,10 +5665,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748103</v>
+        <v>122748122</v>
       </c>
       <c r="B48" t="n">
-        <v>98347</v>
+        <v>92253</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5663,47 +5677,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547389</v>
+        <v>547410</v>
       </c>
       <c r="R48" t="n">
-        <v>6511805</v>
+        <v>6511972</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,11 +5741,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748095</v>
+        <v>122748081</v>
       </c>
       <c r="B49" t="n">
-        <v>91350</v>
+        <v>92260</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5783,38 +5783,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547464</v>
+        <v>547401</v>
       </c>
       <c r="R49" t="n">
-        <v>6511904</v>
+        <v>6511938</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748101</v>
+        <v>122748072</v>
       </c>
       <c r="B50" t="n">
-        <v>5173</v>
+        <v>95126</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5893,34 +5893,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547370</v>
+        <v>547386</v>
       </c>
       <c r="R50" t="n">
-        <v>6511844</v>
+        <v>6511963</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,6 +5953,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5983,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748109</v>
+        <v>122748102</v>
       </c>
       <c r="B51" t="n">
-        <v>92256</v>
+        <v>92260</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6019,14 +6024,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547448</v>
+        <v>547378</v>
       </c>
       <c r="R51" t="n">
-        <v>6511787</v>
+        <v>6511826</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6089,10 +6094,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748122</v>
+        <v>122747992</v>
       </c>
       <c r="B52" t="n">
-        <v>92249</v>
+        <v>92253</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6125,14 +6130,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547410</v>
+        <v>547401</v>
       </c>
       <c r="R52" t="n">
-        <v>6511972</v>
+        <v>6511893</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6165,6 +6170,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6195,10 +6205,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748081</v>
+        <v>122748124</v>
       </c>
       <c r="B53" t="n">
-        <v>92256</v>
+        <v>95126</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6207,38 +6217,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547401</v>
+        <v>547381</v>
       </c>
       <c r="R53" t="n">
-        <v>6511938</v>
+        <v>6511990</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6271,6 +6281,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6301,10 +6316,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748030</v>
+        <v>122748100</v>
       </c>
       <c r="B54" t="n">
-        <v>90940</v>
+        <v>5173</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6313,38 +6328,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547653</v>
+        <v>547368</v>
       </c>
       <c r="R54" t="n">
-        <v>6511677</v>
+        <v>6511855</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,11 +6392,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6412,10 +6422,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748033</v>
+        <v>122748006</v>
       </c>
       <c r="B55" t="n">
-        <v>92256</v>
+        <v>91354</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6424,38 +6434,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547612</v>
+        <v>547516</v>
       </c>
       <c r="R55" t="n">
-        <v>6511812</v>
+        <v>6511927</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6518,10 +6528,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748100</v>
+        <v>122748033</v>
       </c>
       <c r="B56" t="n">
-        <v>5173</v>
+        <v>92260</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6530,38 +6540,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547368</v>
+        <v>547612</v>
       </c>
       <c r="R56" t="n">
-        <v>6511855</v>
+        <v>6511812</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6624,10 +6634,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748001</v>
+        <v>122748077</v>
       </c>
       <c r="B57" t="n">
-        <v>91162</v>
+        <v>79384</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6640,34 +6650,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1101</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547501</v>
+        <v>547364</v>
       </c>
       <c r="R57" t="n">
-        <v>6511967</v>
+        <v>6511915</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6730,10 +6740,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748070</v>
+        <v>122748002</v>
       </c>
       <c r="B58" t="n">
-        <v>90905</v>
+        <v>95126</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6746,34 +6756,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547388</v>
+        <v>547505</v>
       </c>
       <c r="R58" t="n">
-        <v>6511959</v>
+        <v>6511966</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6806,6 +6816,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6836,10 +6851,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748098</v>
+        <v>122748001</v>
       </c>
       <c r="B59" t="n">
-        <v>105453</v>
+        <v>91166</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6848,38 +6863,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>1101</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547433</v>
+        <v>547501</v>
       </c>
       <c r="R59" t="n">
-        <v>6511877</v>
+        <v>6511967</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6942,10 +6957,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748110</v>
+        <v>122748007</v>
       </c>
       <c r="B60" t="n">
-        <v>92221</v>
+        <v>95126</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6958,34 +6973,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547424</v>
+        <v>547554</v>
       </c>
       <c r="R60" t="n">
-        <v>6511755</v>
+        <v>6511871</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7048,10 +7063,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748006</v>
+        <v>122748111</v>
       </c>
       <c r="B61" t="n">
-        <v>91350</v>
+        <v>91567</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7064,34 +7079,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5420</v>
+        <v>6031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547516</v>
+        <v>547434</v>
       </c>
       <c r="R61" t="n">
-        <v>6511927</v>
+        <v>6511758</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7154,10 +7169,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748106</v>
+        <v>122748079</v>
       </c>
       <c r="B62" t="n">
-        <v>92256</v>
+        <v>92251</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7170,34 +7185,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547396</v>
+        <v>547387</v>
       </c>
       <c r="R62" t="n">
-        <v>6511793</v>
+        <v>6511907</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7260,10 +7275,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748097</v>
+        <v>122748106</v>
       </c>
       <c r="B63" t="n">
-        <v>98347</v>
+        <v>92260</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7272,47 +7287,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547426</v>
+        <v>547396</v>
       </c>
       <c r="R63" t="n">
-        <v>6511886</v>
+        <v>6511793</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7345,11 +7351,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7380,10 +7381,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748072</v>
+        <v>122748090</v>
       </c>
       <c r="B64" t="n">
-        <v>95118</v>
+        <v>92260</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7392,38 +7393,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547386</v>
+        <v>547445</v>
       </c>
       <c r="R64" t="n">
-        <v>6511963</v>
+        <v>6511922</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7456,11 +7457,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7494,7 +7490,7 @@
         <v>122748123</v>
       </c>
       <c r="B65" t="n">
-        <v>91563</v>
+        <v>91567</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7597,10 +7593,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748111</v>
+        <v>122748078</v>
       </c>
       <c r="B66" t="n">
-        <v>91563</v>
+        <v>92260</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7609,38 +7605,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547434</v>
+        <v>547386</v>
       </c>
       <c r="R66" t="n">
-        <v>6511758</v>
+        <v>6511902</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7703,10 +7699,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748068</v>
+        <v>122748005</v>
       </c>
       <c r="B67" t="n">
-        <v>95118</v>
+        <v>92260</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7715,38 +7711,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547411</v>
+        <v>547535</v>
       </c>
       <c r="R67" t="n">
-        <v>6511968</v>
+        <v>6511922</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7779,11 +7775,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7814,10 +7805,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748009</v>
+        <v>122748098</v>
       </c>
       <c r="B68" t="n">
-        <v>95118</v>
+        <v>105461</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7830,34 +7821,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547564</v>
+        <v>547433</v>
       </c>
       <c r="R68" t="n">
-        <v>6511874</v>
+        <v>6511877</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7920,10 +7911,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748002</v>
+        <v>122748109</v>
       </c>
       <c r="B69" t="n">
-        <v>95118</v>
+        <v>92260</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7932,38 +7923,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547505</v>
+        <v>547448</v>
       </c>
       <c r="R69" t="n">
-        <v>6511966</v>
+        <v>6511787</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7996,11 +7987,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8031,10 +8017,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748005</v>
+        <v>122748097</v>
       </c>
       <c r="B70" t="n">
-        <v>92256</v>
+        <v>98355</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8043,38 +8029,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547535</v>
+        <v>547426</v>
       </c>
       <c r="R70" t="n">
-        <v>6511922</v>
+        <v>6511886</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8107,6 +8102,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -5877,10 +5877,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748072</v>
+        <v>122748102</v>
       </c>
       <c r="B50" t="n">
-        <v>95126</v>
+        <v>92260</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5889,38 +5889,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547386</v>
+        <v>547378</v>
       </c>
       <c r="R50" t="n">
-        <v>6511963</v>
+        <v>6511826</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,11 +5953,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,10 +5983,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748102</v>
+        <v>122748072</v>
       </c>
       <c r="B51" t="n">
-        <v>92260</v>
+        <v>95126</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6000,38 +5995,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547378</v>
+        <v>547386</v>
       </c>
       <c r="R51" t="n">
-        <v>6511826</v>
+        <v>6511963</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6064,6 +6059,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6634,10 +6634,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748077</v>
+        <v>122748002</v>
       </c>
       <c r="B57" t="n">
-        <v>79384</v>
+        <v>95126</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6646,38 +6646,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547364</v>
+        <v>547505</v>
       </c>
       <c r="R57" t="n">
-        <v>6511915</v>
+        <v>6511966</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6710,6 +6710,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6740,10 +6745,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748002</v>
+        <v>122748077</v>
       </c>
       <c r="B58" t="n">
-        <v>95126</v>
+        <v>79384</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6752,38 +6757,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547505</v>
+        <v>547364</v>
       </c>
       <c r="R58" t="n">
-        <v>6511966</v>
+        <v>6511915</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6816,11 +6821,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7169,10 +7169,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748079</v>
+        <v>122748106</v>
       </c>
       <c r="B62" t="n">
-        <v>92251</v>
+        <v>92260</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7185,34 +7185,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547387</v>
+        <v>547396</v>
       </c>
       <c r="R62" t="n">
-        <v>6511907</v>
+        <v>6511793</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7275,10 +7275,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748106</v>
+        <v>122748079</v>
       </c>
       <c r="B63" t="n">
-        <v>92260</v>
+        <v>92251</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7291,34 +7291,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547396</v>
+        <v>547387</v>
       </c>
       <c r="R63" t="n">
-        <v>6511793</v>
+        <v>6511907</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748009</v>
+        <v>122748101</v>
       </c>
       <c r="B40" t="n">
-        <v>95126</v>
+        <v>5173</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4809,34 +4809,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547564</v>
+        <v>547370</v>
       </c>
       <c r="R40" t="n">
-        <v>6511874</v>
+        <v>6511844</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748068</v>
+        <v>122748124</v>
       </c>
       <c r="B41" t="n">
         <v>95126</v>
@@ -4935,14 +4935,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547411</v>
+        <v>547381</v>
       </c>
       <c r="R41" t="n">
-        <v>6511968</v>
+        <v>6511990</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ca 20 cm i diameter</t>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748103</v>
+        <v>122748106</v>
       </c>
       <c r="B42" t="n">
-        <v>98355</v>
+        <v>92260</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5022,47 +5022,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547389</v>
+        <v>547396</v>
       </c>
       <c r="R42" t="n">
-        <v>6511805</v>
+        <v>6511793</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5095,11 +5086,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5130,10 +5116,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748101</v>
+        <v>122748070</v>
       </c>
       <c r="B43" t="n">
-        <v>5173</v>
+        <v>90909</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5146,34 +5132,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547370</v>
+        <v>547388</v>
       </c>
       <c r="R43" t="n">
-        <v>6511844</v>
+        <v>6511959</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5236,10 +5222,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748095</v>
+        <v>122748098</v>
       </c>
       <c r="B44" t="n">
-        <v>91354</v>
+        <v>105461</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5252,34 +5238,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547464</v>
+        <v>547433</v>
       </c>
       <c r="R44" t="n">
-        <v>6511904</v>
+        <v>6511877</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5342,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748070</v>
+        <v>122748030</v>
       </c>
       <c r="B45" t="n">
-        <v>90909</v>
+        <v>90944</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5354,38 +5340,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547388</v>
+        <v>547653</v>
       </c>
       <c r="R45" t="n">
-        <v>6511959</v>
+        <v>6511677</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5418,6 +5404,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5448,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748030</v>
+        <v>122748002</v>
       </c>
       <c r="B46" t="n">
-        <v>90944</v>
+        <v>95126</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5460,38 +5451,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547653</v>
+        <v>547505</v>
       </c>
       <c r="R46" t="n">
-        <v>6511677</v>
+        <v>6511966</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5528,7 +5519,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På tallåga som hänger mot lodyta</t>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5559,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748110</v>
+        <v>122748081</v>
       </c>
       <c r="B47" t="n">
-        <v>92225</v>
+        <v>92260</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5571,38 +5562,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547424</v>
+        <v>547401</v>
       </c>
       <c r="R47" t="n">
-        <v>6511755</v>
+        <v>6511938</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5665,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748122</v>
+        <v>122748009</v>
       </c>
       <c r="B48" t="n">
-        <v>92253</v>
+        <v>95126</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5677,38 +5668,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547410</v>
+        <v>547564</v>
       </c>
       <c r="R48" t="n">
-        <v>6511972</v>
+        <v>6511874</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5771,10 +5762,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748081</v>
+        <v>122748068</v>
       </c>
       <c r="B49" t="n">
-        <v>92260</v>
+        <v>95126</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5783,38 +5774,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547401</v>
+        <v>547411</v>
       </c>
       <c r="R49" t="n">
-        <v>6511938</v>
+        <v>6511968</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5847,6 +5838,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5983,7 +5979,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748072</v>
+        <v>122748007</v>
       </c>
       <c r="B51" t="n">
         <v>95126</v>
@@ -6023,10 +6019,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547386</v>
+        <v>547554</v>
       </c>
       <c r="R51" t="n">
-        <v>6511963</v>
+        <v>6511871</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6059,11 +6055,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6094,10 +6085,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122747992</v>
+        <v>122748111</v>
       </c>
       <c r="B52" t="n">
-        <v>92253</v>
+        <v>91567</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6106,38 +6097,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>6031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547401</v>
+        <v>547434</v>
       </c>
       <c r="R52" t="n">
-        <v>6511893</v>
+        <v>6511758</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,11 +6161,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6205,10 +6191,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748124</v>
+        <v>122748097</v>
       </c>
       <c r="B53" t="n">
-        <v>95126</v>
+        <v>98355</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6217,38 +6203,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547381</v>
+        <v>547426</v>
       </c>
       <c r="R53" t="n">
-        <v>6511990</v>
+        <v>6511886</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6285,7 +6280,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Större kudde</t>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6316,10 +6311,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748100</v>
+        <v>122748122</v>
       </c>
       <c r="B54" t="n">
-        <v>5173</v>
+        <v>92253</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6328,38 +6323,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>5449</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547368</v>
+        <v>547410</v>
       </c>
       <c r="R54" t="n">
-        <v>6511855</v>
+        <v>6511972</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6422,10 +6417,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748006</v>
+        <v>122748078</v>
       </c>
       <c r="B55" t="n">
-        <v>91354</v>
+        <v>92260</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6434,38 +6429,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547516</v>
+        <v>547386</v>
       </c>
       <c r="R55" t="n">
-        <v>6511927</v>
+        <v>6511902</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6528,7 +6523,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748033</v>
+        <v>122748090</v>
       </c>
       <c r="B56" t="n">
         <v>92260</v>
@@ -6564,14 +6559,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547612</v>
+        <v>547445</v>
       </c>
       <c r="R56" t="n">
-        <v>6511812</v>
+        <v>6511922</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6634,10 +6629,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748002</v>
+        <v>122748006</v>
       </c>
       <c r="B57" t="n">
-        <v>95126</v>
+        <v>91354</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6650,34 +6645,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547505</v>
+        <v>547516</v>
       </c>
       <c r="R57" t="n">
-        <v>6511966</v>
+        <v>6511927</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6710,11 +6705,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6745,10 +6735,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748077</v>
+        <v>122748103</v>
       </c>
       <c r="B58" t="n">
-        <v>79384</v>
+        <v>98355</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6757,38 +6747,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547364</v>
+        <v>547389</v>
       </c>
       <c r="R58" t="n">
-        <v>6511915</v>
+        <v>6511805</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6821,6 +6820,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6851,10 +6855,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748001</v>
+        <v>122748033</v>
       </c>
       <c r="B59" t="n">
-        <v>91166</v>
+        <v>92260</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6867,34 +6871,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1101</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547501</v>
+        <v>547612</v>
       </c>
       <c r="R59" t="n">
-        <v>6511967</v>
+        <v>6511812</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6957,10 +6961,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748007</v>
+        <v>122748123</v>
       </c>
       <c r="B60" t="n">
-        <v>95126</v>
+        <v>91567</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6973,34 +6977,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547554</v>
+        <v>547401</v>
       </c>
       <c r="R60" t="n">
-        <v>6511871</v>
+        <v>6511980</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7063,10 +7067,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748111</v>
+        <v>122748110</v>
       </c>
       <c r="B61" t="n">
-        <v>91567</v>
+        <v>92225</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7079,21 +7083,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7103,10 +7107,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547434</v>
+        <v>547424</v>
       </c>
       <c r="R61" t="n">
-        <v>6511758</v>
+        <v>6511755</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7169,10 +7173,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748106</v>
+        <v>122747992</v>
       </c>
       <c r="B62" t="n">
-        <v>92260</v>
+        <v>92253</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7185,34 +7189,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547396</v>
+        <v>547401</v>
       </c>
       <c r="R62" t="n">
-        <v>6511793</v>
+        <v>6511893</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7245,6 +7249,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7275,10 +7284,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748079</v>
+        <v>122748001</v>
       </c>
       <c r="B63" t="n">
-        <v>92251</v>
+        <v>91166</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7291,34 +7300,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5448</v>
+        <v>1101</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547387</v>
+        <v>547501</v>
       </c>
       <c r="R63" t="n">
-        <v>6511907</v>
+        <v>6511967</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7381,10 +7390,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748090</v>
+        <v>122748095</v>
       </c>
       <c r="B64" t="n">
-        <v>92260</v>
+        <v>91354</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7393,38 +7402,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547445</v>
+        <v>547464</v>
       </c>
       <c r="R64" t="n">
-        <v>6511922</v>
+        <v>6511904</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7487,10 +7496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748123</v>
+        <v>122748109</v>
       </c>
       <c r="B65" t="n">
-        <v>91567</v>
+        <v>92260</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7499,38 +7508,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547401</v>
+        <v>547448</v>
       </c>
       <c r="R65" t="n">
-        <v>6511980</v>
+        <v>6511787</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7593,10 +7602,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748078</v>
+        <v>122748100</v>
       </c>
       <c r="B66" t="n">
-        <v>92260</v>
+        <v>5173</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7605,38 +7614,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547386</v>
+        <v>547368</v>
       </c>
       <c r="R66" t="n">
-        <v>6511902</v>
+        <v>6511855</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7699,10 +7708,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748005</v>
+        <v>122748072</v>
       </c>
       <c r="B67" t="n">
-        <v>92260</v>
+        <v>95126</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7711,38 +7720,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547535</v>
+        <v>547386</v>
       </c>
       <c r="R67" t="n">
-        <v>6511922</v>
+        <v>6511963</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7775,6 +7784,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7805,10 +7819,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748098</v>
+        <v>122748005</v>
       </c>
       <c r="B68" t="n">
-        <v>105461</v>
+        <v>92260</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7817,38 +7831,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547433</v>
+        <v>547535</v>
       </c>
       <c r="R68" t="n">
-        <v>6511877</v>
+        <v>6511922</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7911,10 +7925,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748109</v>
+        <v>122748079</v>
       </c>
       <c r="B69" t="n">
-        <v>92260</v>
+        <v>92251</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7927,34 +7941,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547448</v>
+        <v>547387</v>
       </c>
       <c r="R69" t="n">
-        <v>6511787</v>
+        <v>6511907</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8017,10 +8031,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748097</v>
+        <v>122748077</v>
       </c>
       <c r="B70" t="n">
-        <v>98355</v>
+        <v>79384</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8029,47 +8043,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547426</v>
+        <v>547364</v>
       </c>
       <c r="R70" t="n">
-        <v>6511886</v>
+        <v>6511915</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8102,11 +8107,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748101</v>
+        <v>122748030</v>
       </c>
       <c r="B40" t="n">
-        <v>5173</v>
+        <v>90944</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4805,38 +4805,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547370</v>
+        <v>547653</v>
       </c>
       <c r="R40" t="n">
-        <v>6511844</v>
+        <v>6511677</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4869,6 +4869,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4899,10 +4904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748124</v>
+        <v>122747992</v>
       </c>
       <c r="B41" t="n">
-        <v>95126</v>
+        <v>92253</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4911,38 +4916,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547381</v>
+        <v>547401</v>
       </c>
       <c r="R41" t="n">
-        <v>6511990</v>
+        <v>6511893</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4979,7 +4984,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Större kudde</t>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,7 +5015,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748106</v>
+        <v>122748078</v>
       </c>
       <c r="B42" t="n">
         <v>92260</v>
@@ -5046,14 +5051,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547396</v>
+        <v>547386</v>
       </c>
       <c r="R42" t="n">
-        <v>6511793</v>
+        <v>6511902</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5116,10 +5121,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748070</v>
+        <v>122748106</v>
       </c>
       <c r="B43" t="n">
-        <v>90909</v>
+        <v>92260</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5128,38 +5133,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547388</v>
+        <v>547396</v>
       </c>
       <c r="R43" t="n">
-        <v>6511959</v>
+        <v>6511793</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5222,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748098</v>
+        <v>122748068</v>
       </c>
       <c r="B44" t="n">
-        <v>105461</v>
+        <v>95128</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5238,34 +5243,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547433</v>
+        <v>547411</v>
       </c>
       <c r="R44" t="n">
-        <v>6511877</v>
+        <v>6511968</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5298,6 +5303,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5328,10 +5338,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748030</v>
+        <v>122748095</v>
       </c>
       <c r="B45" t="n">
-        <v>90944</v>
+        <v>91354</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5340,38 +5350,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547653</v>
+        <v>547464</v>
       </c>
       <c r="R45" t="n">
-        <v>6511677</v>
+        <v>6511904</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5404,11 +5414,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5439,10 +5444,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748002</v>
+        <v>122748033</v>
       </c>
       <c r="B46" t="n">
-        <v>95126</v>
+        <v>92260</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5451,38 +5456,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547505</v>
+        <v>547612</v>
       </c>
       <c r="R46" t="n">
-        <v>6511966</v>
+        <v>6511812</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,11 +5520,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,7 +5550,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748081</v>
+        <v>122748005</v>
       </c>
       <c r="B47" t="n">
         <v>92260</v>
@@ -5586,14 +5586,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547401</v>
+        <v>547535</v>
       </c>
       <c r="R47" t="n">
-        <v>6511938</v>
+        <v>6511922</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748009</v>
+        <v>122748110</v>
       </c>
       <c r="B48" t="n">
-        <v>95126</v>
+        <v>92225</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5672,34 +5672,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547564</v>
+        <v>547424</v>
       </c>
       <c r="R48" t="n">
-        <v>6511874</v>
+        <v>6511755</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748068</v>
+        <v>122748001</v>
       </c>
       <c r="B49" t="n">
-        <v>95126</v>
+        <v>91166</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5774,38 +5774,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547411</v>
+        <v>547501</v>
       </c>
       <c r="R49" t="n">
-        <v>6511968</v>
+        <v>6511967</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5838,11 +5838,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5873,10 +5868,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748102</v>
+        <v>122748097</v>
       </c>
       <c r="B50" t="n">
-        <v>92260</v>
+        <v>98357</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5885,38 +5880,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547378</v>
+        <v>547426</v>
       </c>
       <c r="R50" t="n">
-        <v>6511826</v>
+        <v>6511886</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,6 +5953,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5979,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748007</v>
+        <v>122748103</v>
       </c>
       <c r="B51" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5991,38 +6000,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547554</v>
+        <v>547389</v>
       </c>
       <c r="R51" t="n">
-        <v>6511871</v>
+        <v>6511805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,6 +6073,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,7 +6108,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748111</v>
+        <v>122748123</v>
       </c>
       <c r="B52" t="n">
         <v>91567</v>
@@ -6121,14 +6144,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547434</v>
+        <v>547401</v>
       </c>
       <c r="R52" t="n">
-        <v>6511758</v>
+        <v>6511980</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6191,10 +6214,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748097</v>
+        <v>122748006</v>
       </c>
       <c r="B53" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6203,47 +6226,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547426</v>
+        <v>547516</v>
       </c>
       <c r="R53" t="n">
-        <v>6511886</v>
+        <v>6511927</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6276,11 +6290,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6311,10 +6320,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748122</v>
+        <v>122748081</v>
       </c>
       <c r="B54" t="n">
-        <v>92253</v>
+        <v>92260</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6327,34 +6336,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547410</v>
+        <v>547401</v>
       </c>
       <c r="R54" t="n">
-        <v>6511972</v>
+        <v>6511938</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6417,10 +6426,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748078</v>
+        <v>122748124</v>
       </c>
       <c r="B55" t="n">
-        <v>92260</v>
+        <v>95128</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6429,38 +6438,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547386</v>
+        <v>547381</v>
       </c>
       <c r="R55" t="n">
-        <v>6511902</v>
+        <v>6511990</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6493,6 +6502,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6523,7 +6537,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748090</v>
+        <v>122748102</v>
       </c>
       <c r="B56" t="n">
         <v>92260</v>
@@ -6559,14 +6573,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547445</v>
+        <v>547378</v>
       </c>
       <c r="R56" t="n">
-        <v>6511922</v>
+        <v>6511826</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6629,10 +6643,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748006</v>
+        <v>122748100</v>
       </c>
       <c r="B57" t="n">
-        <v>91354</v>
+        <v>5173</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6645,34 +6659,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547516</v>
+        <v>547368</v>
       </c>
       <c r="R57" t="n">
-        <v>6511927</v>
+        <v>6511855</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6735,10 +6749,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748103</v>
+        <v>122748111</v>
       </c>
       <c r="B58" t="n">
-        <v>98355</v>
+        <v>91567</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6747,47 +6761,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547389</v>
+        <v>547434</v>
       </c>
       <c r="R58" t="n">
-        <v>6511805</v>
+        <v>6511758</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6820,11 +6825,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6855,10 +6855,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748033</v>
+        <v>122748122</v>
       </c>
       <c r="B59" t="n">
-        <v>92260</v>
+        <v>92253</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6871,34 +6871,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547612</v>
+        <v>547410</v>
       </c>
       <c r="R59" t="n">
-        <v>6511812</v>
+        <v>6511972</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748123</v>
+        <v>122748098</v>
       </c>
       <c r="B60" t="n">
-        <v>91567</v>
+        <v>105463</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6977,34 +6977,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6031</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547401</v>
+        <v>547433</v>
       </c>
       <c r="R60" t="n">
-        <v>6511980</v>
+        <v>6511877</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7067,10 +7067,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748110</v>
+        <v>122748072</v>
       </c>
       <c r="B61" t="n">
-        <v>92225</v>
+        <v>95128</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7083,34 +7083,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547424</v>
+        <v>547386</v>
       </c>
       <c r="R61" t="n">
-        <v>6511755</v>
+        <v>6511963</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7143,6 +7143,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7173,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122747992</v>
+        <v>122748070</v>
       </c>
       <c r="B62" t="n">
-        <v>92253</v>
+        <v>90909</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7185,38 +7190,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547401</v>
+        <v>547388</v>
       </c>
       <c r="R62" t="n">
-        <v>6511893</v>
+        <v>6511959</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7249,11 +7254,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7284,10 +7284,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748001</v>
+        <v>122748109</v>
       </c>
       <c r="B63" t="n">
-        <v>91166</v>
+        <v>92260</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7300,34 +7300,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1101</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547501</v>
+        <v>547448</v>
       </c>
       <c r="R63" t="n">
-        <v>6511967</v>
+        <v>6511787</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7390,10 +7390,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748095</v>
+        <v>122748090</v>
       </c>
       <c r="B64" t="n">
-        <v>91354</v>
+        <v>92260</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7402,38 +7402,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547464</v>
+        <v>547445</v>
       </c>
       <c r="R64" t="n">
-        <v>6511904</v>
+        <v>6511922</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748109</v>
+        <v>122748079</v>
       </c>
       <c r="B65" t="n">
-        <v>92260</v>
+        <v>92251</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7512,34 +7512,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547448</v>
+        <v>547387</v>
       </c>
       <c r="R65" t="n">
-        <v>6511787</v>
+        <v>6511907</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748100</v>
+        <v>122748009</v>
       </c>
       <c r="B66" t="n">
-        <v>5173</v>
+        <v>95128</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7618,34 +7618,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547368</v>
+        <v>547564</v>
       </c>
       <c r="R66" t="n">
-        <v>6511855</v>
+        <v>6511874</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7708,10 +7708,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748072</v>
+        <v>122748007</v>
       </c>
       <c r="B67" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547386</v>
+        <v>547554</v>
       </c>
       <c r="R67" t="n">
-        <v>6511963</v>
+        <v>6511871</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7784,11 +7784,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7819,10 +7814,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748005</v>
+        <v>122748002</v>
       </c>
       <c r="B68" t="n">
-        <v>92260</v>
+        <v>95128</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7831,25 +7826,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7859,10 +7854,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547535</v>
+        <v>547505</v>
       </c>
       <c r="R68" t="n">
-        <v>6511922</v>
+        <v>6511966</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7895,6 +7890,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7925,10 +7925,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748079</v>
+        <v>122748077</v>
       </c>
       <c r="B69" t="n">
-        <v>92251</v>
+        <v>79384</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7941,21 +7941,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547387</v>
+        <v>547364</v>
       </c>
       <c r="R69" t="n">
-        <v>6511907</v>
+        <v>6511915</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8031,10 +8031,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748077</v>
+        <v>122748101</v>
       </c>
       <c r="B70" t="n">
-        <v>79384</v>
+        <v>5173</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8043,38 +8043,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547364</v>
+        <v>547370</v>
       </c>
       <c r="R70" t="n">
-        <v>6511915</v>
+        <v>6511844</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -6643,10 +6643,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748100</v>
+        <v>122748111</v>
       </c>
       <c r="B57" t="n">
-        <v>5173</v>
+        <v>91567</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6659,21 +6659,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>6031</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6683,10 +6683,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547368</v>
+        <v>547434</v>
       </c>
       <c r="R57" t="n">
-        <v>6511855</v>
+        <v>6511758</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748111</v>
+        <v>122748122</v>
       </c>
       <c r="B58" t="n">
-        <v>91567</v>
+        <v>92253</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6761,38 +6761,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547434</v>
+        <v>547410</v>
       </c>
       <c r="R58" t="n">
-        <v>6511758</v>
+        <v>6511972</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6855,10 +6855,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748122</v>
+        <v>122748100</v>
       </c>
       <c r="B59" t="n">
-        <v>92253</v>
+        <v>5173</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6867,38 +6867,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547410</v>
+        <v>547368</v>
       </c>
       <c r="R59" t="n">
-        <v>6511972</v>
+        <v>6511855</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -5444,10 +5444,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748033</v>
+        <v>122748097</v>
       </c>
       <c r="B46" t="n">
-        <v>92260</v>
+        <v>98357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5456,38 +5456,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547612</v>
+        <v>547426</v>
       </c>
       <c r="R46" t="n">
-        <v>6511812</v>
+        <v>6511886</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5520,6 +5529,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5564,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748005</v>
+        <v>122748103</v>
       </c>
       <c r="B47" t="n">
-        <v>92260</v>
+        <v>98357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5562,38 +5576,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547535</v>
+        <v>547389</v>
       </c>
       <c r="R47" t="n">
-        <v>6511922</v>
+        <v>6511805</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5626,6 +5649,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5656,10 +5684,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748110</v>
+        <v>122748001</v>
       </c>
       <c r="B48" t="n">
-        <v>92225</v>
+        <v>91166</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5668,38 +5696,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>1101</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547424</v>
+        <v>547501</v>
       </c>
       <c r="R48" t="n">
-        <v>6511755</v>
+        <v>6511967</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5762,10 +5790,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748001</v>
+        <v>122748033</v>
       </c>
       <c r="B49" t="n">
-        <v>91166</v>
+        <v>92260</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5778,34 +5806,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1101</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547501</v>
+        <v>547612</v>
       </c>
       <c r="R49" t="n">
-        <v>6511967</v>
+        <v>6511812</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5868,10 +5896,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748097</v>
+        <v>122748005</v>
       </c>
       <c r="B50" t="n">
-        <v>98357</v>
+        <v>92260</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5880,47 +5908,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547426</v>
+        <v>547535</v>
       </c>
       <c r="R50" t="n">
-        <v>6511886</v>
+        <v>6511922</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,11 +5972,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,10 +6002,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748103</v>
+        <v>122748110</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>92225</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6000,47 +6014,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547389</v>
+        <v>547424</v>
       </c>
       <c r="R51" t="n">
-        <v>6511805</v>
+        <v>6511755</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6073,11 +6078,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748030</v>
+        <v>122748072</v>
       </c>
       <c r="B40" t="n">
-        <v>90944</v>
+        <v>95128</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4805,38 +4805,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547653</v>
+        <v>547386</v>
       </c>
       <c r="R40" t="n">
-        <v>6511677</v>
+        <v>6511963</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På tallåga som hänger mot lodyta</t>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4904,10 +4904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122747992</v>
+        <v>122748081</v>
       </c>
       <c r="B41" t="n">
-        <v>92253</v>
+        <v>92260</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4920,34 +4920,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>547401</v>
       </c>
       <c r="R41" t="n">
-        <v>6511893</v>
+        <v>6511938</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,11 +4980,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5015,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748078</v>
+        <v>122748111</v>
       </c>
       <c r="B42" t="n">
-        <v>92260</v>
+        <v>91567</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5027,38 +5022,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547386</v>
+        <v>547434</v>
       </c>
       <c r="R42" t="n">
-        <v>6511902</v>
+        <v>6511758</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5121,7 +5116,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748106</v>
+        <v>122748102</v>
       </c>
       <c r="B43" t="n">
         <v>92260</v>
@@ -5157,14 +5152,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547396</v>
+        <v>547378</v>
       </c>
       <c r="R43" t="n">
-        <v>6511793</v>
+        <v>6511826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,10 +5222,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748068</v>
+        <v>122748095</v>
       </c>
       <c r="B44" t="n">
-        <v>95128</v>
+        <v>91354</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5243,34 +5238,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547411</v>
+        <v>547464</v>
       </c>
       <c r="R44" t="n">
-        <v>6511968</v>
+        <v>6511904</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,11 +5298,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5338,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748095</v>
+        <v>122748103</v>
       </c>
       <c r="B45" t="n">
-        <v>91354</v>
+        <v>98357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5350,38 +5340,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547464</v>
+        <v>547389</v>
       </c>
       <c r="R45" t="n">
-        <v>6511904</v>
+        <v>6511805</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5414,6 +5413,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5444,10 +5448,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748097</v>
+        <v>122748030</v>
       </c>
       <c r="B46" t="n">
-        <v>98357</v>
+        <v>90944</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5456,47 +5460,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547426</v>
+        <v>547653</v>
       </c>
       <c r="R46" t="n">
-        <v>6511886</v>
+        <v>6511677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5533,7 +5528,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>51 plantor</t>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5564,10 +5559,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748103</v>
+        <v>122748079</v>
       </c>
       <c r="B47" t="n">
-        <v>98357</v>
+        <v>92251</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5576,47 +5571,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547389</v>
+        <v>547387</v>
       </c>
       <c r="R47" t="n">
-        <v>6511805</v>
+        <v>6511907</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5649,11 +5635,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5684,10 +5665,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748001</v>
+        <v>122748002</v>
       </c>
       <c r="B48" t="n">
-        <v>91166</v>
+        <v>95128</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5696,38 +5677,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547501</v>
+        <v>547505</v>
       </c>
       <c r="R48" t="n">
-        <v>6511967</v>
+        <v>6511966</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5760,6 +5741,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5790,10 +5776,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748033</v>
+        <v>122748077</v>
       </c>
       <c r="B49" t="n">
-        <v>92260</v>
+        <v>79384</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5806,34 +5792,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547612</v>
+        <v>547364</v>
       </c>
       <c r="R49" t="n">
-        <v>6511812</v>
+        <v>6511915</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5896,10 +5882,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748005</v>
+        <v>122748009</v>
       </c>
       <c r="B50" t="n">
-        <v>92260</v>
+        <v>95128</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5908,38 +5894,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547535</v>
+        <v>547564</v>
       </c>
       <c r="R50" t="n">
-        <v>6511922</v>
+        <v>6511874</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6002,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748110</v>
+        <v>122748078</v>
       </c>
       <c r="B51" t="n">
-        <v>92225</v>
+        <v>92260</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6014,38 +6000,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547424</v>
+        <v>547386</v>
       </c>
       <c r="R51" t="n">
-        <v>6511755</v>
+        <v>6511902</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6108,10 +6094,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748123</v>
+        <v>122748001</v>
       </c>
       <c r="B52" t="n">
-        <v>91567</v>
+        <v>91166</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6120,38 +6106,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6031</v>
+        <v>1101</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547401</v>
+        <v>547501</v>
       </c>
       <c r="R52" t="n">
-        <v>6511980</v>
+        <v>6511967</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6214,10 +6200,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748006</v>
+        <v>122748109</v>
       </c>
       <c r="B53" t="n">
-        <v>91354</v>
+        <v>92260</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6226,38 +6212,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547516</v>
+        <v>547448</v>
       </c>
       <c r="R53" t="n">
-        <v>6511927</v>
+        <v>6511787</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6320,10 +6306,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748081</v>
+        <v>122748097</v>
       </c>
       <c r="B54" t="n">
-        <v>92260</v>
+        <v>98357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6332,38 +6318,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547401</v>
+        <v>547426</v>
       </c>
       <c r="R54" t="n">
-        <v>6511938</v>
+        <v>6511886</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6396,6 +6391,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6426,10 +6426,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748124</v>
+        <v>122747992</v>
       </c>
       <c r="B55" t="n">
-        <v>95128</v>
+        <v>92253</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6438,38 +6438,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547381</v>
+        <v>547401</v>
       </c>
       <c r="R55" t="n">
-        <v>6511990</v>
+        <v>6511893</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Större kudde</t>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6537,7 +6537,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748102</v>
+        <v>122748090</v>
       </c>
       <c r="B56" t="n">
         <v>92260</v>
@@ -6573,14 +6573,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547378</v>
+        <v>547445</v>
       </c>
       <c r="R56" t="n">
-        <v>6511826</v>
+        <v>6511922</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6643,10 +6643,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748111</v>
+        <v>122748033</v>
       </c>
       <c r="B57" t="n">
-        <v>91567</v>
+        <v>92260</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6655,38 +6655,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547434</v>
+        <v>547612</v>
       </c>
       <c r="R57" t="n">
-        <v>6511758</v>
+        <v>6511812</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6855,10 +6855,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748100</v>
+        <v>122748006</v>
       </c>
       <c r="B59" t="n">
-        <v>5173</v>
+        <v>91354</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6871,34 +6871,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547368</v>
+        <v>547516</v>
       </c>
       <c r="R59" t="n">
-        <v>6511855</v>
+        <v>6511927</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748098</v>
+        <v>122748124</v>
       </c>
       <c r="B60" t="n">
-        <v>105463</v>
+        <v>95128</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6977,34 +6977,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547433</v>
+        <v>547381</v>
       </c>
       <c r="R60" t="n">
-        <v>6511877</v>
+        <v>6511990</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7037,6 +7037,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7067,10 +7072,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748072</v>
+        <v>122748123</v>
       </c>
       <c r="B61" t="n">
-        <v>95128</v>
+        <v>91567</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7083,34 +7088,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547386</v>
+        <v>547401</v>
       </c>
       <c r="R61" t="n">
-        <v>6511963</v>
+        <v>6511980</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7143,11 +7148,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7284,10 +7284,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748109</v>
+        <v>122748100</v>
       </c>
       <c r="B63" t="n">
-        <v>92260</v>
+        <v>5173</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7296,38 +7296,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547448</v>
+        <v>547368</v>
       </c>
       <c r="R63" t="n">
-        <v>6511787</v>
+        <v>6511855</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7390,10 +7390,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748090</v>
+        <v>122748101</v>
       </c>
       <c r="B64" t="n">
-        <v>92260</v>
+        <v>5173</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7402,38 +7402,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547445</v>
+        <v>547370</v>
       </c>
       <c r="R64" t="n">
-        <v>6511922</v>
+        <v>6511844</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748079</v>
+        <v>122748098</v>
       </c>
       <c r="B65" t="n">
-        <v>92251</v>
+        <v>105463</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7508,38 +7508,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5448</v>
+        <v>221144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547387</v>
+        <v>547433</v>
       </c>
       <c r="R65" t="n">
-        <v>6511907</v>
+        <v>6511877</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748009</v>
+        <v>122748068</v>
       </c>
       <c r="B66" t="n">
         <v>95128</v>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547564</v>
+        <v>547411</v>
       </c>
       <c r="R66" t="n">
-        <v>6511874</v>
+        <v>6511968</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7678,6 +7678,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7708,10 +7713,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748007</v>
+        <v>122748005</v>
       </c>
       <c r="B67" t="n">
-        <v>95128</v>
+        <v>92260</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7720,38 +7725,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547554</v>
+        <v>547535</v>
       </c>
       <c r="R67" t="n">
-        <v>6511871</v>
+        <v>6511922</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7814,10 +7819,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748002</v>
+        <v>122748110</v>
       </c>
       <c r="B68" t="n">
-        <v>95128</v>
+        <v>92225</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7830,34 +7835,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547505</v>
+        <v>547424</v>
       </c>
       <c r="R68" t="n">
-        <v>6511966</v>
+        <v>6511755</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7890,11 +7895,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7925,10 +7925,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748077</v>
+        <v>122748007</v>
       </c>
       <c r="B69" t="n">
-        <v>79384</v>
+        <v>95128</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7937,38 +7937,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547364</v>
+        <v>547554</v>
       </c>
       <c r="R69" t="n">
-        <v>6511915</v>
+        <v>6511871</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8031,10 +8031,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748101</v>
+        <v>122748106</v>
       </c>
       <c r="B70" t="n">
-        <v>5173</v>
+        <v>92260</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8043,38 +8043,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547370</v>
+        <v>547396</v>
       </c>
       <c r="R70" t="n">
-        <v>6511844</v>
+        <v>6511793</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -5665,7 +5665,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748002</v>
+        <v>122748009</v>
       </c>
       <c r="B48" t="n">
         <v>95128</v>
@@ -5701,14 +5701,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547505</v>
+        <v>547564</v>
       </c>
       <c r="R48" t="n">
-        <v>6511966</v>
+        <v>6511874</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,11 +5741,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5776,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748077</v>
+        <v>122748002</v>
       </c>
       <c r="B49" t="n">
-        <v>79384</v>
+        <v>95128</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5788,38 +5783,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547364</v>
+        <v>547505</v>
       </c>
       <c r="R49" t="n">
-        <v>6511915</v>
+        <v>6511966</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5852,6 +5847,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5882,10 +5882,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748009</v>
+        <v>122748078</v>
       </c>
       <c r="B50" t="n">
-        <v>95128</v>
+        <v>92260</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5894,38 +5894,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547564</v>
+        <v>547386</v>
       </c>
       <c r="R50" t="n">
-        <v>6511874</v>
+        <v>6511902</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5988,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748078</v>
+        <v>122748077</v>
       </c>
       <c r="B51" t="n">
-        <v>92260</v>
+        <v>79384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547386</v>
+        <v>547364</v>
       </c>
       <c r="R51" t="n">
-        <v>6511902</v>
+        <v>6511915</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748068</v>
+        <v>122748005</v>
       </c>
       <c r="B66" t="n">
-        <v>95128</v>
+        <v>92260</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7614,38 +7614,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547411</v>
+        <v>547535</v>
       </c>
       <c r="R66" t="n">
-        <v>6511968</v>
+        <v>6511922</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7678,11 +7678,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7713,10 +7708,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748005</v>
+        <v>122748068</v>
       </c>
       <c r="B67" t="n">
-        <v>92260</v>
+        <v>95128</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7725,38 +7720,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547535</v>
+        <v>547411</v>
       </c>
       <c r="R67" t="n">
-        <v>6511922</v>
+        <v>6511968</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7789,6 +7784,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -5665,7 +5665,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748009</v>
+        <v>122748002</v>
       </c>
       <c r="B48" t="n">
         <v>95128</v>
@@ -5701,14 +5701,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547564</v>
+        <v>547505</v>
       </c>
       <c r="R48" t="n">
-        <v>6511874</v>
+        <v>6511966</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,6 +5741,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,10 +5776,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748002</v>
+        <v>122748077</v>
       </c>
       <c r="B49" t="n">
-        <v>95128</v>
+        <v>79384</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5783,38 +5788,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547505</v>
+        <v>547364</v>
       </c>
       <c r="R49" t="n">
-        <v>6511966</v>
+        <v>6511915</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5847,11 +5852,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5882,10 +5882,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748078</v>
+        <v>122748009</v>
       </c>
       <c r="B50" t="n">
-        <v>92260</v>
+        <v>95128</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5894,38 +5894,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547386</v>
+        <v>547564</v>
       </c>
       <c r="R50" t="n">
-        <v>6511902</v>
+        <v>6511874</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5988,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748077</v>
+        <v>122748078</v>
       </c>
       <c r="B51" t="n">
-        <v>79384</v>
+        <v>92260</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547364</v>
+        <v>547386</v>
       </c>
       <c r="R51" t="n">
-        <v>6511915</v>
+        <v>6511902</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6094,10 +6094,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748001</v>
+        <v>122748109</v>
       </c>
       <c r="B52" t="n">
-        <v>91166</v>
+        <v>92260</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6110,34 +6110,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1101</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547501</v>
+        <v>547448</v>
       </c>
       <c r="R52" t="n">
-        <v>6511967</v>
+        <v>6511787</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6200,10 +6200,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748109</v>
+        <v>122748001</v>
       </c>
       <c r="B53" t="n">
-        <v>92260</v>
+        <v>91166</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6216,34 +6216,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>1101</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547448</v>
+        <v>547501</v>
       </c>
       <c r="R53" t="n">
-        <v>6511787</v>
+        <v>6511967</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748072</v>
+        <v>122748081</v>
       </c>
       <c r="B40" t="n">
-        <v>95128</v>
+        <v>92268</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4805,38 +4805,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547386</v>
+        <v>547401</v>
       </c>
       <c r="R40" t="n">
-        <v>6511963</v>
+        <v>6511938</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4869,11 +4869,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4904,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748081</v>
+        <v>122748009</v>
       </c>
       <c r="B41" t="n">
-        <v>92260</v>
+        <v>95136</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4916,38 +4911,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547401</v>
+        <v>547564</v>
       </c>
       <c r="R41" t="n">
-        <v>6511938</v>
+        <v>6511874</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5013,7 +5008,7 @@
         <v>122748111</v>
       </c>
       <c r="B42" t="n">
-        <v>91567</v>
+        <v>91575</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5116,10 +5111,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748102</v>
+        <v>122748110</v>
       </c>
       <c r="B43" t="n">
-        <v>92260</v>
+        <v>92233</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5128,25 +5123,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5156,10 +5151,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547378</v>
+        <v>547424</v>
       </c>
       <c r="R43" t="n">
-        <v>6511826</v>
+        <v>6511755</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5222,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748095</v>
+        <v>122748098</v>
       </c>
       <c r="B44" t="n">
-        <v>91354</v>
+        <v>105471</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5238,34 +5233,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547464</v>
+        <v>547433</v>
       </c>
       <c r="R44" t="n">
-        <v>6511904</v>
+        <v>6511877</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5328,10 +5323,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748103</v>
+        <v>122748106</v>
       </c>
       <c r="B45" t="n">
-        <v>98357</v>
+        <v>92268</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5340,47 +5335,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547389</v>
+        <v>547396</v>
       </c>
       <c r="R45" t="n">
-        <v>6511805</v>
+        <v>6511793</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,11 +5399,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5448,10 +5429,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748030</v>
+        <v>122748077</v>
       </c>
       <c r="B46" t="n">
-        <v>90944</v>
+        <v>79384</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5464,34 +5445,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547653</v>
+        <v>547364</v>
       </c>
       <c r="R46" t="n">
-        <v>6511677</v>
+        <v>6511915</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5524,11 +5505,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5559,10 +5535,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748079</v>
+        <v>122748002</v>
       </c>
       <c r="B47" t="n">
-        <v>92251</v>
+        <v>95136</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5571,38 +5547,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5448</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547387</v>
+        <v>547505</v>
       </c>
       <c r="R47" t="n">
-        <v>6511907</v>
+        <v>6511966</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,6 +5611,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5665,10 +5646,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748002</v>
+        <v>122747992</v>
       </c>
       <c r="B48" t="n">
-        <v>95128</v>
+        <v>92261</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5677,38 +5658,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547505</v>
+        <v>547401</v>
       </c>
       <c r="R48" t="n">
-        <v>6511966</v>
+        <v>6511893</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5745,7 +5726,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt längs stigen</t>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5776,10 +5757,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748077</v>
+        <v>122748109</v>
       </c>
       <c r="B49" t="n">
-        <v>79384</v>
+        <v>92268</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5792,34 +5773,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547364</v>
+        <v>547448</v>
       </c>
       <c r="R49" t="n">
-        <v>6511915</v>
+        <v>6511787</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5882,10 +5863,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748009</v>
+        <v>122748005</v>
       </c>
       <c r="B50" t="n">
-        <v>95128</v>
+        <v>92268</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5894,38 +5875,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547564</v>
+        <v>547535</v>
       </c>
       <c r="R50" t="n">
-        <v>6511874</v>
+        <v>6511922</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5988,10 +5969,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748078</v>
+        <v>122748070</v>
       </c>
       <c r="B51" t="n">
-        <v>92260</v>
+        <v>90917</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6000,38 +5981,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547386</v>
+        <v>547388</v>
       </c>
       <c r="R51" t="n">
-        <v>6511902</v>
+        <v>6511959</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6094,10 +6075,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748109</v>
+        <v>122748123</v>
       </c>
       <c r="B52" t="n">
-        <v>92260</v>
+        <v>91575</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6106,38 +6087,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547448</v>
+        <v>547401</v>
       </c>
       <c r="R52" t="n">
-        <v>6511787</v>
+        <v>6511980</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6200,10 +6181,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748001</v>
+        <v>122748102</v>
       </c>
       <c r="B53" t="n">
-        <v>91166</v>
+        <v>92268</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6216,34 +6197,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1101</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547501</v>
+        <v>547378</v>
       </c>
       <c r="R53" t="n">
-        <v>6511967</v>
+        <v>6511826</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6306,10 +6287,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748097</v>
+        <v>122748006</v>
       </c>
       <c r="B54" t="n">
-        <v>98357</v>
+        <v>91362</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6318,47 +6299,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547426</v>
+        <v>547516</v>
       </c>
       <c r="R54" t="n">
-        <v>6511886</v>
+        <v>6511927</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6391,11 +6363,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6426,10 +6393,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122747992</v>
+        <v>122748001</v>
       </c>
       <c r="B55" t="n">
-        <v>92253</v>
+        <v>91174</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6442,21 +6409,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6466,10 +6433,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547401</v>
+        <v>547501</v>
       </c>
       <c r="R55" t="n">
-        <v>6511893</v>
+        <v>6511967</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6502,11 +6469,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6537,10 +6499,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748090</v>
+        <v>122748124</v>
       </c>
       <c r="B56" t="n">
-        <v>92260</v>
+        <v>95136</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6549,38 +6511,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547445</v>
+        <v>547381</v>
       </c>
       <c r="R56" t="n">
-        <v>6511922</v>
+        <v>6511990</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6613,6 +6575,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6643,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748033</v>
+        <v>122748030</v>
       </c>
       <c r="B57" t="n">
-        <v>92260</v>
+        <v>90952</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6659,34 +6626,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547612</v>
+        <v>547653</v>
       </c>
       <c r="R57" t="n">
-        <v>6511812</v>
+        <v>6511677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6719,6 +6686,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6752,7 +6724,7 @@
         <v>122748122</v>
       </c>
       <c r="B58" t="n">
-        <v>92253</v>
+        <v>92261</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6855,10 +6827,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748006</v>
+        <v>122748007</v>
       </c>
       <c r="B59" t="n">
-        <v>91354</v>
+        <v>95136</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6871,21 +6843,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6895,10 +6867,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547516</v>
+        <v>547554</v>
       </c>
       <c r="R59" t="n">
-        <v>6511927</v>
+        <v>6511871</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6961,10 +6933,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748124</v>
+        <v>122748079</v>
       </c>
       <c r="B60" t="n">
-        <v>95128</v>
+        <v>92259</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6973,38 +6945,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2180</v>
+        <v>5448</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547381</v>
+        <v>547387</v>
       </c>
       <c r="R60" t="n">
-        <v>6511990</v>
+        <v>6511907</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7037,11 +7009,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7072,10 +7039,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748123</v>
+        <v>122748100</v>
       </c>
       <c r="B61" t="n">
-        <v>91567</v>
+        <v>5173</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7088,34 +7055,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6031</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547401</v>
+        <v>547368</v>
       </c>
       <c r="R61" t="n">
-        <v>6511980</v>
+        <v>6511855</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7178,10 +7145,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748070</v>
+        <v>122748068</v>
       </c>
       <c r="B62" t="n">
-        <v>90909</v>
+        <v>95136</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7194,21 +7161,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7218,10 +7185,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547388</v>
+        <v>547411</v>
       </c>
       <c r="R62" t="n">
-        <v>6511959</v>
+        <v>6511968</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7254,6 +7221,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7284,10 +7256,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748100</v>
+        <v>122748072</v>
       </c>
       <c r="B63" t="n">
-        <v>5173</v>
+        <v>95136</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7300,34 +7272,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547368</v>
+        <v>547386</v>
       </c>
       <c r="R63" t="n">
-        <v>6511855</v>
+        <v>6511963</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7360,6 +7332,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7390,10 +7367,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748101</v>
+        <v>122748097</v>
       </c>
       <c r="B64" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7402,38 +7379,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547370</v>
+        <v>547426</v>
       </c>
       <c r="R64" t="n">
-        <v>6511844</v>
+        <v>6511886</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7466,6 +7452,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7496,10 +7487,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748098</v>
+        <v>122748078</v>
       </c>
       <c r="B65" t="n">
-        <v>105463</v>
+        <v>92268</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7508,38 +7499,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547433</v>
+        <v>547386</v>
       </c>
       <c r="R65" t="n">
-        <v>6511877</v>
+        <v>6511902</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7602,10 +7593,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748005</v>
+        <v>122748101</v>
       </c>
       <c r="B66" t="n">
-        <v>92260</v>
+        <v>5173</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7614,38 +7605,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547535</v>
+        <v>547370</v>
       </c>
       <c r="R66" t="n">
-        <v>6511922</v>
+        <v>6511844</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7708,10 +7699,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748068</v>
+        <v>122748095</v>
       </c>
       <c r="B67" t="n">
-        <v>95128</v>
+        <v>91362</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7724,34 +7715,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547411</v>
+        <v>547464</v>
       </c>
       <c r="R67" t="n">
-        <v>6511968</v>
+        <v>6511904</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7784,11 +7775,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7819,10 +7805,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748110</v>
+        <v>122748033</v>
       </c>
       <c r="B68" t="n">
-        <v>92225</v>
+        <v>92268</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7831,38 +7817,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547424</v>
+        <v>547612</v>
       </c>
       <c r="R68" t="n">
-        <v>6511755</v>
+        <v>6511812</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7925,10 +7911,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748007</v>
+        <v>122748090</v>
       </c>
       <c r="B69" t="n">
-        <v>95128</v>
+        <v>92268</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7937,38 +7923,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547554</v>
+        <v>547445</v>
       </c>
       <c r="R69" t="n">
-        <v>6511871</v>
+        <v>6511922</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8031,10 +8017,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748106</v>
+        <v>122748103</v>
       </c>
       <c r="B70" t="n">
-        <v>92260</v>
+        <v>98365</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8043,38 +8029,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547396</v>
+        <v>547389</v>
       </c>
       <c r="R70" t="n">
-        <v>6511793</v>
+        <v>6511805</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8107,6 +8102,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -5323,10 +5323,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748106</v>
+        <v>122748077</v>
       </c>
       <c r="B45" t="n">
-        <v>92268</v>
+        <v>79384</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5339,34 +5339,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547396</v>
+        <v>547364</v>
       </c>
       <c r="R45" t="n">
-        <v>6511793</v>
+        <v>6511915</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5429,10 +5429,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748077</v>
+        <v>122748106</v>
       </c>
       <c r="B46" t="n">
-        <v>79384</v>
+        <v>92268</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5445,34 +5445,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547364</v>
+        <v>547396</v>
       </c>
       <c r="R46" t="n">
-        <v>6511915</v>
+        <v>6511793</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748081</v>
+        <v>122748009</v>
       </c>
       <c r="B40" t="n">
-        <v>92268</v>
+        <v>95136</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4805,38 +4805,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547401</v>
+        <v>547564</v>
       </c>
       <c r="R40" t="n">
-        <v>6511938</v>
+        <v>6511874</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748009</v>
+        <v>122748122</v>
       </c>
       <c r="B41" t="n">
-        <v>95136</v>
+        <v>92261</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4911,38 +4911,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547564</v>
+        <v>547410</v>
       </c>
       <c r="R41" t="n">
-        <v>6511874</v>
+        <v>6511972</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5005,10 +5005,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748111</v>
+        <v>122748101</v>
       </c>
       <c r="B42" t="n">
-        <v>91575</v>
+        <v>5173</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5021,21 +5021,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6031</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547434</v>
+        <v>547370</v>
       </c>
       <c r="R42" t="n">
-        <v>6511758</v>
+        <v>6511844</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5111,10 +5111,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748110</v>
+        <v>122748033</v>
       </c>
       <c r="B43" t="n">
-        <v>92233</v>
+        <v>92268</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5123,38 +5123,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547424</v>
+        <v>547612</v>
       </c>
       <c r="R43" t="n">
-        <v>6511755</v>
+        <v>6511812</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748098</v>
+        <v>122748006</v>
       </c>
       <c r="B44" t="n">
-        <v>105471</v>
+        <v>91362</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5233,34 +5233,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547433</v>
+        <v>547516</v>
       </c>
       <c r="R44" t="n">
-        <v>6511877</v>
+        <v>6511927</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5323,10 +5323,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748077</v>
+        <v>122747992</v>
       </c>
       <c r="B45" t="n">
-        <v>79384</v>
+        <v>92261</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5339,34 +5339,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547364</v>
+        <v>547401</v>
       </c>
       <c r="R45" t="n">
-        <v>6511915</v>
+        <v>6511893</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,6 +5399,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5429,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748106</v>
+        <v>122748123</v>
       </c>
       <c r="B46" t="n">
-        <v>92268</v>
+        <v>91575</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5441,38 +5446,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547396</v>
+        <v>547401</v>
       </c>
       <c r="R46" t="n">
-        <v>6511793</v>
+        <v>6511980</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5535,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748002</v>
+        <v>122748097</v>
       </c>
       <c r="B47" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5547,38 +5552,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547505</v>
+        <v>547426</v>
       </c>
       <c r="R47" t="n">
-        <v>6511966</v>
+        <v>6511886</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5615,7 +5629,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt längs stigen</t>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5646,10 +5660,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122747992</v>
+        <v>122748077</v>
       </c>
       <c r="B48" t="n">
-        <v>92261</v>
+        <v>79384</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5662,34 +5676,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547401</v>
+        <v>547364</v>
       </c>
       <c r="R48" t="n">
-        <v>6511893</v>
+        <v>6511915</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5722,11 +5736,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5863,10 +5872,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748005</v>
+        <v>122748095</v>
       </c>
       <c r="B50" t="n">
-        <v>92268</v>
+        <v>91362</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5875,38 +5884,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547535</v>
+        <v>547464</v>
       </c>
       <c r="R50" t="n">
-        <v>6511922</v>
+        <v>6511904</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5969,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748070</v>
+        <v>122748110</v>
       </c>
       <c r="B51" t="n">
-        <v>90917</v>
+        <v>92233</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5985,34 +5994,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547388</v>
+        <v>547424</v>
       </c>
       <c r="R51" t="n">
-        <v>6511959</v>
+        <v>6511755</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6075,10 +6084,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748123</v>
+        <v>122748068</v>
       </c>
       <c r="B52" t="n">
-        <v>91575</v>
+        <v>95136</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6091,34 +6100,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547401</v>
+        <v>547411</v>
       </c>
       <c r="R52" t="n">
-        <v>6511980</v>
+        <v>6511968</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6151,6 +6160,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6181,10 +6195,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748102</v>
+        <v>122748030</v>
       </c>
       <c r="B53" t="n">
-        <v>92268</v>
+        <v>90952</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6197,34 +6211,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547378</v>
+        <v>547653</v>
       </c>
       <c r="R53" t="n">
-        <v>6511826</v>
+        <v>6511677</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6257,6 +6271,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6287,10 +6306,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748006</v>
+        <v>122748081</v>
       </c>
       <c r="B54" t="n">
-        <v>91362</v>
+        <v>92268</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6299,38 +6318,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547516</v>
+        <v>547401</v>
       </c>
       <c r="R54" t="n">
-        <v>6511927</v>
+        <v>6511938</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6393,10 +6412,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748001</v>
+        <v>122748072</v>
       </c>
       <c r="B55" t="n">
-        <v>91174</v>
+        <v>95136</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6405,38 +6424,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547501</v>
+        <v>547386</v>
       </c>
       <c r="R55" t="n">
-        <v>6511967</v>
+        <v>6511963</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6469,6 +6488,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6499,10 +6523,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748124</v>
+        <v>122748103</v>
       </c>
       <c r="B56" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6511,38 +6535,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547381</v>
+        <v>547389</v>
       </c>
       <c r="R56" t="n">
-        <v>6511990</v>
+        <v>6511805</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6579,7 +6612,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Större kudde</t>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6610,10 +6643,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748030</v>
+        <v>122748090</v>
       </c>
       <c r="B57" t="n">
-        <v>90952</v>
+        <v>92268</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6626,34 +6659,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547653</v>
+        <v>547445</v>
       </c>
       <c r="R57" t="n">
-        <v>6511677</v>
+        <v>6511922</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6686,11 +6719,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6721,10 +6749,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748122</v>
+        <v>122748106</v>
       </c>
       <c r="B58" t="n">
-        <v>92261</v>
+        <v>92268</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6737,34 +6765,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547410</v>
+        <v>547396</v>
       </c>
       <c r="R58" t="n">
-        <v>6511972</v>
+        <v>6511793</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6933,10 +6961,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748079</v>
+        <v>122748005</v>
       </c>
       <c r="B60" t="n">
-        <v>92259</v>
+        <v>92268</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6949,34 +6977,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547387</v>
+        <v>547535</v>
       </c>
       <c r="R60" t="n">
-        <v>6511907</v>
+        <v>6511922</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7039,10 +7067,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748100</v>
+        <v>122748124</v>
       </c>
       <c r="B61" t="n">
-        <v>5173</v>
+        <v>95136</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7055,34 +7083,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547368</v>
+        <v>547381</v>
       </c>
       <c r="R61" t="n">
-        <v>6511855</v>
+        <v>6511990</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7115,6 +7143,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7145,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748068</v>
+        <v>122748078</v>
       </c>
       <c r="B62" t="n">
-        <v>95136</v>
+        <v>92268</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7157,38 +7190,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547411</v>
+        <v>547386</v>
       </c>
       <c r="R62" t="n">
-        <v>6511968</v>
+        <v>6511902</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7221,11 +7254,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7256,10 +7284,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748072</v>
+        <v>122748001</v>
       </c>
       <c r="B63" t="n">
-        <v>95136</v>
+        <v>91174</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7268,38 +7296,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547386</v>
+        <v>547501</v>
       </c>
       <c r="R63" t="n">
-        <v>6511963</v>
+        <v>6511967</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7332,11 +7360,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7367,10 +7390,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748097</v>
+        <v>122748070</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7379,47 +7402,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547426</v>
+        <v>547388</v>
       </c>
       <c r="R64" t="n">
-        <v>6511886</v>
+        <v>6511959</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7452,11 +7466,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7487,10 +7496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748078</v>
+        <v>122748002</v>
       </c>
       <c r="B65" t="n">
-        <v>92268</v>
+        <v>95136</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7499,38 +7508,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547386</v>
+        <v>547505</v>
       </c>
       <c r="R65" t="n">
-        <v>6511902</v>
+        <v>6511966</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7563,6 +7572,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7593,10 +7607,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748101</v>
+        <v>122748098</v>
       </c>
       <c r="B66" t="n">
-        <v>5173</v>
+        <v>105471</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7609,34 +7623,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547370</v>
+        <v>547433</v>
       </c>
       <c r="R66" t="n">
-        <v>6511844</v>
+        <v>6511877</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7699,10 +7713,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748095</v>
+        <v>122748079</v>
       </c>
       <c r="B67" t="n">
-        <v>91362</v>
+        <v>92259</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7711,38 +7725,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5420</v>
+        <v>5448</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547464</v>
+        <v>547387</v>
       </c>
       <c r="R67" t="n">
-        <v>6511904</v>
+        <v>6511907</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7805,10 +7819,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748033</v>
+        <v>122748100</v>
       </c>
       <c r="B68" t="n">
-        <v>92268</v>
+        <v>5173</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7817,38 +7831,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547612</v>
+        <v>547368</v>
       </c>
       <c r="R68" t="n">
-        <v>6511812</v>
+        <v>6511855</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7911,10 +7925,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748090</v>
+        <v>122748111</v>
       </c>
       <c r="B69" t="n">
-        <v>92268</v>
+        <v>91575</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7923,38 +7937,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547445</v>
+        <v>547434</v>
       </c>
       <c r="R69" t="n">
-        <v>6511922</v>
+        <v>6511758</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8017,10 +8031,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748103</v>
+        <v>122748102</v>
       </c>
       <c r="B70" t="n">
-        <v>98365</v>
+        <v>92268</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8029,47 +8043,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547389</v>
+        <v>547378</v>
       </c>
       <c r="R70" t="n">
-        <v>6511805</v>
+        <v>6511826</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8102,11 +8107,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748097</v>
+        <v>122748077</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>79384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,47 +5552,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547426</v>
+        <v>547364</v>
       </c>
       <c r="R47" t="n">
-        <v>6511886</v>
+        <v>6511915</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,11 +5616,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5660,10 +5646,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748077</v>
+        <v>122748097</v>
       </c>
       <c r="B48" t="n">
-        <v>79384</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5672,38 +5658,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547364</v>
+        <v>547426</v>
       </c>
       <c r="R48" t="n">
-        <v>6511915</v>
+        <v>6511886</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,6 +5731,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5872,10 +5872,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748095</v>
+        <v>122748110</v>
       </c>
       <c r="B50" t="n">
-        <v>91362</v>
+        <v>92233</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5888,34 +5888,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547464</v>
+        <v>547424</v>
       </c>
       <c r="R50" t="n">
-        <v>6511904</v>
+        <v>6511755</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5978,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748110</v>
+        <v>122748095</v>
       </c>
       <c r="B51" t="n">
-        <v>92233</v>
+        <v>91362</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5994,34 +5994,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547424</v>
+        <v>547464</v>
       </c>
       <c r="R51" t="n">
-        <v>6511755</v>
+        <v>6511904</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7390,10 +7390,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748070</v>
+        <v>122748098</v>
       </c>
       <c r="B64" t="n">
-        <v>90917</v>
+        <v>105471</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7406,34 +7406,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547388</v>
+        <v>547433</v>
       </c>
       <c r="R64" t="n">
-        <v>6511959</v>
+        <v>6511877</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748002</v>
+        <v>122748070</v>
       </c>
       <c r="B65" t="n">
-        <v>95136</v>
+        <v>90917</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7512,34 +7512,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547505</v>
+        <v>547388</v>
       </c>
       <c r="R65" t="n">
-        <v>6511966</v>
+        <v>6511959</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7572,11 +7572,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7607,10 +7602,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748098</v>
+        <v>122748002</v>
       </c>
       <c r="B66" t="n">
-        <v>105471</v>
+        <v>95136</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7623,34 +7618,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547433</v>
+        <v>547505</v>
       </c>
       <c r="R66" t="n">
-        <v>6511877</v>
+        <v>6511966</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7683,6 +7678,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748077</v>
+        <v>122748097</v>
       </c>
       <c r="B47" t="n">
-        <v>79384</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,38 +5552,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547364</v>
+        <v>547426</v>
       </c>
       <c r="R47" t="n">
-        <v>6511915</v>
+        <v>6511886</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5616,6 +5625,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5646,10 +5660,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748097</v>
+        <v>122748077</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>79384</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5658,47 +5672,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547426</v>
+        <v>547364</v>
       </c>
       <c r="R48" t="n">
-        <v>6511886</v>
+        <v>6511915</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,11 +5736,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5872,10 +5872,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748110</v>
+        <v>122748095</v>
       </c>
       <c r="B50" t="n">
-        <v>92233</v>
+        <v>91362</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5888,34 +5888,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547424</v>
+        <v>547464</v>
       </c>
       <c r="R50" t="n">
-        <v>6511755</v>
+        <v>6511904</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5978,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748095</v>
+        <v>122748110</v>
       </c>
       <c r="B51" t="n">
-        <v>91362</v>
+        <v>92233</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5994,34 +5994,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547464</v>
+        <v>547424</v>
       </c>
       <c r="R51" t="n">
-        <v>6511904</v>
+        <v>6511755</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748009</v>
+        <v>122748006</v>
       </c>
       <c r="B40" t="n">
-        <v>95136</v>
+        <v>91362</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4809,21 +4809,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547564</v>
+        <v>547516</v>
       </c>
       <c r="R40" t="n">
-        <v>6511874</v>
+        <v>6511927</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748122</v>
+        <v>122748079</v>
       </c>
       <c r="B41" t="n">
-        <v>92261</v>
+        <v>92259</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4915,34 +4915,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547410</v>
+        <v>547387</v>
       </c>
       <c r="R41" t="n">
-        <v>6511972</v>
+        <v>6511907</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5111,10 +5111,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748033</v>
+        <v>122748001</v>
       </c>
       <c r="B43" t="n">
-        <v>92268</v>
+        <v>91174</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5127,34 +5127,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>1101</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547612</v>
+        <v>547501</v>
       </c>
       <c r="R43" t="n">
-        <v>6511812</v>
+        <v>6511967</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748006</v>
+        <v>122748007</v>
       </c>
       <c r="B44" t="n">
-        <v>91362</v>
+        <v>95136</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5233,21 +5233,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547516</v>
+        <v>547554</v>
       </c>
       <c r="R44" t="n">
-        <v>6511927</v>
+        <v>6511871</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5323,10 +5323,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122747992</v>
+        <v>122748030</v>
       </c>
       <c r="B45" t="n">
-        <v>92261</v>
+        <v>90952</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5339,34 +5339,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547401</v>
+        <v>547653</v>
       </c>
       <c r="R45" t="n">
-        <v>6511893</v>
+        <v>6511677</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Väster om stigen</t>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5434,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748123</v>
+        <v>122748081</v>
       </c>
       <c r="B46" t="n">
-        <v>91575</v>
+        <v>92268</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5446,38 +5446,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>547401</v>
       </c>
       <c r="R46" t="n">
-        <v>6511980</v>
+        <v>6511938</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748097</v>
+        <v>122748122</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>92261</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,47 +5552,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547426</v>
+        <v>547410</v>
       </c>
       <c r="R47" t="n">
-        <v>6511886</v>
+        <v>6511972</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,11 +5616,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5660,10 +5646,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748077</v>
+        <v>122748005</v>
       </c>
       <c r="B48" t="n">
-        <v>79384</v>
+        <v>92268</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5676,34 +5662,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547364</v>
+        <v>547535</v>
       </c>
       <c r="R48" t="n">
-        <v>6511915</v>
+        <v>6511922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5766,10 +5752,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748109</v>
+        <v>122748124</v>
       </c>
       <c r="B49" t="n">
-        <v>92268</v>
+        <v>95136</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5778,38 +5764,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547448</v>
+        <v>547381</v>
       </c>
       <c r="R49" t="n">
-        <v>6511787</v>
+        <v>6511990</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5842,6 +5828,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5872,10 +5863,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748095</v>
+        <v>122748002</v>
       </c>
       <c r="B50" t="n">
-        <v>91362</v>
+        <v>95136</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5888,34 +5879,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547464</v>
+        <v>547505</v>
       </c>
       <c r="R50" t="n">
-        <v>6511904</v>
+        <v>6511966</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,6 +5939,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5974,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748110</v>
+        <v>122747992</v>
       </c>
       <c r="B51" t="n">
-        <v>92233</v>
+        <v>92261</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5990,38 +5986,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547424</v>
+        <v>547401</v>
       </c>
       <c r="R51" t="n">
-        <v>6511755</v>
+        <v>6511893</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6054,6 +6050,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6084,10 +6085,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748068</v>
+        <v>122748109</v>
       </c>
       <c r="B52" t="n">
-        <v>95136</v>
+        <v>92268</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6096,38 +6097,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547411</v>
+        <v>547448</v>
       </c>
       <c r="R52" t="n">
-        <v>6511968</v>
+        <v>6511787</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6160,11 +6161,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6195,10 +6191,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748030</v>
+        <v>122748095</v>
       </c>
       <c r="B53" t="n">
-        <v>90952</v>
+        <v>91362</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6207,38 +6203,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547653</v>
+        <v>547464</v>
       </c>
       <c r="R53" t="n">
-        <v>6511677</v>
+        <v>6511904</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6271,11 +6267,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6306,10 +6297,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748081</v>
+        <v>122748100</v>
       </c>
       <c r="B54" t="n">
-        <v>92268</v>
+        <v>5173</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6318,38 +6309,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547401</v>
+        <v>547368</v>
       </c>
       <c r="R54" t="n">
-        <v>6511938</v>
+        <v>6511855</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6412,10 +6403,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748072</v>
+        <v>122748097</v>
       </c>
       <c r="B55" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6424,38 +6415,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547386</v>
+        <v>547426</v>
       </c>
       <c r="R55" t="n">
-        <v>6511963</v>
+        <v>6511886</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Flera lite större kuddar.</t>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6643,10 +6643,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748090</v>
+        <v>122748098</v>
       </c>
       <c r="B57" t="n">
-        <v>92268</v>
+        <v>105471</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6655,38 +6655,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547445</v>
+        <v>547433</v>
       </c>
       <c r="R57" t="n">
-        <v>6511922</v>
+        <v>6511877</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748106</v>
+        <v>122748077</v>
       </c>
       <c r="B58" t="n">
-        <v>92268</v>
+        <v>79384</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6765,34 +6765,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547396</v>
+        <v>547364</v>
       </c>
       <c r="R58" t="n">
-        <v>6511793</v>
+        <v>6511915</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6855,10 +6855,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748007</v>
+        <v>122748033</v>
       </c>
       <c r="B59" t="n">
-        <v>95136</v>
+        <v>92268</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6867,38 +6867,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547554</v>
+        <v>547612</v>
       </c>
       <c r="R59" t="n">
-        <v>6511871</v>
+        <v>6511812</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748005</v>
+        <v>122748068</v>
       </c>
       <c r="B60" t="n">
-        <v>92268</v>
+        <v>95136</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6973,38 +6973,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547535</v>
+        <v>547411</v>
       </c>
       <c r="R60" t="n">
-        <v>6511922</v>
+        <v>6511968</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7037,6 +7037,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7067,10 +7072,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748124</v>
+        <v>122748090</v>
       </c>
       <c r="B61" t="n">
-        <v>95136</v>
+        <v>92268</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7079,38 +7084,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547381</v>
+        <v>547445</v>
       </c>
       <c r="R61" t="n">
-        <v>6511990</v>
+        <v>6511922</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7143,11 +7148,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748078</v>
+        <v>122748111</v>
       </c>
       <c r="B62" t="n">
-        <v>92268</v>
+        <v>91575</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7190,38 +7190,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547386</v>
+        <v>547434</v>
       </c>
       <c r="R62" t="n">
-        <v>6511902</v>
+        <v>6511758</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7284,10 +7284,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748001</v>
+        <v>122748110</v>
       </c>
       <c r="B63" t="n">
-        <v>91174</v>
+        <v>92233</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7296,38 +7296,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1101</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547501</v>
+        <v>547424</v>
       </c>
       <c r="R63" t="n">
-        <v>6511967</v>
+        <v>6511755</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7390,10 +7390,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748098</v>
+        <v>122748102</v>
       </c>
       <c r="B64" t="n">
-        <v>105471</v>
+        <v>92268</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7402,38 +7402,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547433</v>
+        <v>547378</v>
       </c>
       <c r="R64" t="n">
-        <v>6511877</v>
+        <v>6511826</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748070</v>
+        <v>122748009</v>
       </c>
       <c r="B65" t="n">
-        <v>90917</v>
+        <v>95136</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7512,21 +7512,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547388</v>
+        <v>547564</v>
       </c>
       <c r="R65" t="n">
-        <v>6511959</v>
+        <v>6511874</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748002</v>
+        <v>122748123</v>
       </c>
       <c r="B66" t="n">
-        <v>95136</v>
+        <v>91575</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7618,34 +7618,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547505</v>
+        <v>547401</v>
       </c>
       <c r="R66" t="n">
-        <v>6511966</v>
+        <v>6511980</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7678,11 +7678,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7713,10 +7708,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748079</v>
+        <v>122748070</v>
       </c>
       <c r="B67" t="n">
-        <v>92259</v>
+        <v>90917</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7725,38 +7720,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547387</v>
+        <v>547388</v>
       </c>
       <c r="R67" t="n">
-        <v>6511907</v>
+        <v>6511959</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7819,10 +7814,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748100</v>
+        <v>122748072</v>
       </c>
       <c r="B68" t="n">
-        <v>5173</v>
+        <v>95136</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7835,34 +7830,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547368</v>
+        <v>547386</v>
       </c>
       <c r="R68" t="n">
-        <v>6511855</v>
+        <v>6511963</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7895,6 +7890,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7925,10 +7925,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748111</v>
+        <v>122748078</v>
       </c>
       <c r="B69" t="n">
-        <v>91575</v>
+        <v>92268</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7937,38 +7937,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547434</v>
+        <v>547386</v>
       </c>
       <c r="R69" t="n">
-        <v>6511758</v>
+        <v>6511902</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8031,7 +8031,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748102</v>
+        <v>122748106</v>
       </c>
       <c r="B70" t="n">
         <v>92268</v>
@@ -8067,14 +8067,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547378</v>
+        <v>547396</v>
       </c>
       <c r="R70" t="n">
-        <v>6511826</v>
+        <v>6511793</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,7 +4793,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748006</v>
+        <v>122748095</v>
       </c>
       <c r="B40" t="n">
         <v>91362</v>
@@ -4829,14 +4829,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547516</v>
+        <v>547464</v>
       </c>
       <c r="R40" t="n">
-        <v>6511927</v>
+        <v>6511904</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748079</v>
+        <v>122748103</v>
       </c>
       <c r="B41" t="n">
-        <v>92259</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4911,38 +4911,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547387</v>
+        <v>547389</v>
       </c>
       <c r="R41" t="n">
-        <v>6511907</v>
+        <v>6511805</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4975,6 +4984,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748101</v>
+        <v>122748097</v>
       </c>
       <c r="B42" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,38 +5031,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547370</v>
+        <v>547426</v>
       </c>
       <c r="R42" t="n">
-        <v>6511844</v>
+        <v>6511886</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5081,6 +5104,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5111,10 +5139,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748001</v>
+        <v>122748090</v>
       </c>
       <c r="B43" t="n">
-        <v>91174</v>
+        <v>92268</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5127,34 +5155,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1101</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547501</v>
+        <v>547445</v>
       </c>
       <c r="R43" t="n">
-        <v>6511967</v>
+        <v>6511922</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5217,10 +5245,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748007</v>
+        <v>122748081</v>
       </c>
       <c r="B44" t="n">
-        <v>95136</v>
+        <v>92268</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5229,38 +5257,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547554</v>
+        <v>547401</v>
       </c>
       <c r="R44" t="n">
-        <v>6511871</v>
+        <v>6511938</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5323,10 +5351,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748030</v>
+        <v>122748079</v>
       </c>
       <c r="B45" t="n">
-        <v>90952</v>
+        <v>92259</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5339,34 +5367,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>5448</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547653</v>
+        <v>547387</v>
       </c>
       <c r="R45" t="n">
-        <v>6511677</v>
+        <v>6511907</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,11 +5427,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5434,7 +5457,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748081</v>
+        <v>122748033</v>
       </c>
       <c r="B46" t="n">
         <v>92268</v>
@@ -5470,14 +5493,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547401</v>
+        <v>547612</v>
       </c>
       <c r="R46" t="n">
-        <v>6511938</v>
+        <v>6511812</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5540,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748122</v>
+        <v>122748109</v>
       </c>
       <c r="B47" t="n">
-        <v>92261</v>
+        <v>92268</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5556,34 +5579,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547410</v>
+        <v>547448</v>
       </c>
       <c r="R47" t="n">
-        <v>6511972</v>
+        <v>6511787</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5752,10 +5775,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748124</v>
+        <v>122748110</v>
       </c>
       <c r="B49" t="n">
-        <v>95136</v>
+        <v>92233</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5768,34 +5791,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547381</v>
+        <v>547424</v>
       </c>
       <c r="R49" t="n">
-        <v>6511990</v>
+        <v>6511755</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5828,11 +5851,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5863,7 +5881,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748002</v>
+        <v>122748072</v>
       </c>
       <c r="B50" t="n">
         <v>95136</v>
@@ -5899,14 +5917,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547505</v>
+        <v>547386</v>
       </c>
       <c r="R50" t="n">
-        <v>6511966</v>
+        <v>6511963</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5943,7 +5961,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt längs stigen</t>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5974,10 +5992,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122747992</v>
+        <v>122748030</v>
       </c>
       <c r="B51" t="n">
-        <v>92261</v>
+        <v>90952</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5990,34 +6008,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547401</v>
+        <v>547653</v>
       </c>
       <c r="R51" t="n">
-        <v>6511893</v>
+        <v>6511677</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6054,7 +6072,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Väster om stigen</t>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,7 +6103,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748109</v>
+        <v>122748106</v>
       </c>
       <c r="B52" t="n">
         <v>92268</v>
@@ -6121,14 +6139,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547448</v>
+        <v>547396</v>
       </c>
       <c r="R52" t="n">
-        <v>6511787</v>
+        <v>6511793</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6191,10 +6209,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748095</v>
+        <v>122748122</v>
       </c>
       <c r="B53" t="n">
-        <v>91362</v>
+        <v>92261</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6203,38 +6221,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5420</v>
+        <v>5449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547464</v>
+        <v>547410</v>
       </c>
       <c r="R53" t="n">
-        <v>6511904</v>
+        <v>6511972</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6297,10 +6315,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748100</v>
+        <v>122748001</v>
       </c>
       <c r="B54" t="n">
-        <v>5173</v>
+        <v>91174</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6309,38 +6327,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>1101</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547368</v>
+        <v>547501</v>
       </c>
       <c r="R54" t="n">
-        <v>6511855</v>
+        <v>6511967</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6403,10 +6421,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748097</v>
+        <v>122748070</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6415,47 +6433,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547426</v>
+        <v>547388</v>
       </c>
       <c r="R55" t="n">
-        <v>6511886</v>
+        <v>6511959</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,11 +6497,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6523,10 +6527,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748103</v>
+        <v>122748124</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6535,47 +6539,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547389</v>
+        <v>547381</v>
       </c>
       <c r="R56" t="n">
-        <v>6511805</v>
+        <v>6511990</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6612,7 +6607,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>9 plantor</t>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6643,10 +6638,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748098</v>
+        <v>122748102</v>
       </c>
       <c r="B57" t="n">
-        <v>105471</v>
+        <v>92268</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6655,38 +6650,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547433</v>
+        <v>547378</v>
       </c>
       <c r="R57" t="n">
-        <v>6511877</v>
+        <v>6511826</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6749,10 +6744,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748077</v>
+        <v>122748007</v>
       </c>
       <c r="B58" t="n">
-        <v>79384</v>
+        <v>95136</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6761,38 +6756,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547364</v>
+        <v>547554</v>
       </c>
       <c r="R58" t="n">
-        <v>6511915</v>
+        <v>6511871</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6855,10 +6850,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748033</v>
+        <v>122748101</v>
       </c>
       <c r="B59" t="n">
-        <v>92268</v>
+        <v>5173</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6867,38 +6862,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547612</v>
+        <v>547370</v>
       </c>
       <c r="R59" t="n">
-        <v>6511812</v>
+        <v>6511844</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6961,10 +6956,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748068</v>
+        <v>122748100</v>
       </c>
       <c r="B60" t="n">
-        <v>95136</v>
+        <v>5173</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6977,34 +6972,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547411</v>
+        <v>547368</v>
       </c>
       <c r="R60" t="n">
-        <v>6511968</v>
+        <v>6511855</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7037,11 +7032,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7072,10 +7062,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748090</v>
+        <v>122748123</v>
       </c>
       <c r="B61" t="n">
-        <v>92268</v>
+        <v>91575</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7084,38 +7074,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547445</v>
+        <v>547401</v>
       </c>
       <c r="R61" t="n">
-        <v>6511922</v>
+        <v>6511980</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7178,10 +7168,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748111</v>
+        <v>122747992</v>
       </c>
       <c r="B62" t="n">
-        <v>91575</v>
+        <v>92261</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7190,38 +7180,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547434</v>
+        <v>547401</v>
       </c>
       <c r="R62" t="n">
-        <v>6511758</v>
+        <v>6511893</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7254,6 +7244,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7284,10 +7279,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748110</v>
+        <v>122748002</v>
       </c>
       <c r="B63" t="n">
-        <v>92233</v>
+        <v>95136</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7300,34 +7295,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547424</v>
+        <v>547505</v>
       </c>
       <c r="R63" t="n">
-        <v>6511755</v>
+        <v>6511966</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7360,6 +7355,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7390,10 +7390,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748102</v>
+        <v>122748009</v>
       </c>
       <c r="B64" t="n">
-        <v>92268</v>
+        <v>95136</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7402,38 +7402,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547378</v>
+        <v>547564</v>
       </c>
       <c r="R64" t="n">
-        <v>6511826</v>
+        <v>6511874</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748009</v>
+        <v>122748111</v>
       </c>
       <c r="B65" t="n">
-        <v>95136</v>
+        <v>91575</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7512,34 +7512,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547564</v>
+        <v>547434</v>
       </c>
       <c r="R65" t="n">
-        <v>6511874</v>
+        <v>6511758</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748123</v>
+        <v>122748098</v>
       </c>
       <c r="B66" t="n">
-        <v>91575</v>
+        <v>105471</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7618,34 +7618,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6031</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547401</v>
+        <v>547433</v>
       </c>
       <c r="R66" t="n">
-        <v>6511980</v>
+        <v>6511877</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7708,10 +7708,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748070</v>
+        <v>122748006</v>
       </c>
       <c r="B67" t="n">
-        <v>90917</v>
+        <v>91362</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7724,21 +7724,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>5420</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547388</v>
+        <v>547516</v>
       </c>
       <c r="R67" t="n">
-        <v>6511959</v>
+        <v>6511927</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7814,7 +7814,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748072</v>
+        <v>122748068</v>
       </c>
       <c r="B68" t="n">
         <v>95136</v>
@@ -7854,10 +7854,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547386</v>
+        <v>547411</v>
       </c>
       <c r="R68" t="n">
-        <v>6511963</v>
+        <v>6511968</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Flera lite större kuddar.</t>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7925,10 +7925,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748078</v>
+        <v>122748077</v>
       </c>
       <c r="B69" t="n">
-        <v>92268</v>
+        <v>79384</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7941,21 +7941,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547386</v>
+        <v>547364</v>
       </c>
       <c r="R69" t="n">
-        <v>6511902</v>
+        <v>6511915</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8031,7 +8031,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748106</v>
+        <v>122748078</v>
       </c>
       <c r="B70" t="n">
         <v>92268</v>
@@ -8067,14 +8067,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547396</v>
+        <v>547386</v>
       </c>
       <c r="R70" t="n">
-        <v>6511793</v>
+        <v>6511902</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -5019,10 +5019,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748097</v>
+        <v>122748090</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>92268</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5031,47 +5031,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547426</v>
+        <v>547445</v>
       </c>
       <c r="R42" t="n">
-        <v>6511886</v>
+        <v>6511922</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5104,11 +5095,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5139,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748090</v>
+        <v>122748097</v>
       </c>
       <c r="B43" t="n">
-        <v>92268</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5151,38 +5137,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547445</v>
+        <v>547426</v>
       </c>
       <c r="R43" t="n">
-        <v>6511922</v>
+        <v>6511886</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5215,6 +5210,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6421,10 +6421,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748070</v>
+        <v>122748124</v>
       </c>
       <c r="B55" t="n">
-        <v>90917</v>
+        <v>95136</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6437,34 +6437,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547388</v>
+        <v>547381</v>
       </c>
       <c r="R55" t="n">
-        <v>6511959</v>
+        <v>6511990</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6497,6 +6497,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6527,10 +6532,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748124</v>
+        <v>122748070</v>
       </c>
       <c r="B56" t="n">
-        <v>95136</v>
+        <v>90917</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6543,34 +6548,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547381</v>
+        <v>547388</v>
       </c>
       <c r="R56" t="n">
-        <v>6511990</v>
+        <v>6511959</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6603,11 +6608,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7390,10 +7390,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748009</v>
+        <v>122748111</v>
       </c>
       <c r="B64" t="n">
-        <v>95136</v>
+        <v>91575</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7406,34 +7406,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547564</v>
+        <v>547434</v>
       </c>
       <c r="R64" t="n">
-        <v>6511874</v>
+        <v>6511758</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7496,10 +7496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748111</v>
+        <v>122748098</v>
       </c>
       <c r="B65" t="n">
-        <v>91575</v>
+        <v>105471</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7512,34 +7512,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6031</v>
+        <v>221144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547434</v>
+        <v>547433</v>
       </c>
       <c r="R65" t="n">
-        <v>6511758</v>
+        <v>6511877</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748098</v>
+        <v>122748009</v>
       </c>
       <c r="B66" t="n">
-        <v>105471</v>
+        <v>95136</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7618,34 +7618,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547433</v>
+        <v>547564</v>
       </c>
       <c r="R66" t="n">
-        <v>6511877</v>
+        <v>6511874</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -6421,10 +6421,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748124</v>
+        <v>122748070</v>
       </c>
       <c r="B55" t="n">
-        <v>95136</v>
+        <v>90917</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6437,34 +6437,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547381</v>
+        <v>547388</v>
       </c>
       <c r="R55" t="n">
-        <v>6511990</v>
+        <v>6511959</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6497,11 +6497,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6532,10 +6527,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748070</v>
+        <v>122748124</v>
       </c>
       <c r="B56" t="n">
-        <v>90917</v>
+        <v>95136</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6548,34 +6543,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547388</v>
+        <v>547381</v>
       </c>
       <c r="R56" t="n">
-        <v>6511959</v>
+        <v>6511990</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6608,6 +6603,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748095</v>
+        <v>122748033</v>
       </c>
       <c r="B40" t="n">
-        <v>91362</v>
+        <v>92271</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4805,38 +4805,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547464</v>
+        <v>547612</v>
       </c>
       <c r="R40" t="n">
-        <v>6511904</v>
+        <v>6511812</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748103</v>
+        <v>122748077</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>79387</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4911,47 +4911,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547389</v>
+        <v>547364</v>
       </c>
       <c r="R41" t="n">
-        <v>6511805</v>
+        <v>6511915</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4984,11 +4975,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5019,10 +5005,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748090</v>
+        <v>122748030</v>
       </c>
       <c r="B42" t="n">
-        <v>92268</v>
+        <v>90955</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5035,34 +5021,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547445</v>
+        <v>547653</v>
       </c>
       <c r="R42" t="n">
-        <v>6511922</v>
+        <v>6511677</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5095,6 +5081,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5125,10 +5116,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748097</v>
+        <v>122748009</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5137,47 +5128,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547426</v>
+        <v>547564</v>
       </c>
       <c r="R43" t="n">
-        <v>6511886</v>
+        <v>6511874</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5210,11 +5192,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5245,10 +5222,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748081</v>
+        <v>122748110</v>
       </c>
       <c r="B44" t="n">
-        <v>92268</v>
+        <v>92236</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5257,38 +5234,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547401</v>
+        <v>547424</v>
       </c>
       <c r="R44" t="n">
-        <v>6511938</v>
+        <v>6511755</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5351,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748079</v>
+        <v>122748095</v>
       </c>
       <c r="B45" t="n">
-        <v>92259</v>
+        <v>91365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5363,38 +5340,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5448</v>
+        <v>5420</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547387</v>
+        <v>547464</v>
       </c>
       <c r="R45" t="n">
-        <v>6511907</v>
+        <v>6511904</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5457,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748033</v>
+        <v>122748070</v>
       </c>
       <c r="B46" t="n">
-        <v>92268</v>
+        <v>90920</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5469,38 +5446,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547612</v>
+        <v>547388</v>
       </c>
       <c r="R46" t="n">
-        <v>6511812</v>
+        <v>6511959</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5563,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748109</v>
+        <v>122747992</v>
       </c>
       <c r="B47" t="n">
-        <v>92268</v>
+        <v>92264</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5579,34 +5556,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547448</v>
+        <v>547401</v>
       </c>
       <c r="R47" t="n">
-        <v>6511787</v>
+        <v>6511893</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5639,6 +5616,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,10 +5651,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748005</v>
+        <v>122748103</v>
       </c>
       <c r="B48" t="n">
-        <v>92268</v>
+        <v>98368</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5681,38 +5663,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547535</v>
+        <v>547389</v>
       </c>
       <c r="R48" t="n">
-        <v>6511922</v>
+        <v>6511805</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5745,6 +5736,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5775,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748110</v>
+        <v>122748102</v>
       </c>
       <c r="B49" t="n">
-        <v>92233</v>
+        <v>92271</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5787,25 +5783,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5815,10 +5811,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547424</v>
+        <v>547378</v>
       </c>
       <c r="R49" t="n">
-        <v>6511755</v>
+        <v>6511826</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5881,10 +5877,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748072</v>
+        <v>122748007</v>
       </c>
       <c r="B50" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5921,10 +5917,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547386</v>
+        <v>547554</v>
       </c>
       <c r="R50" t="n">
-        <v>6511963</v>
+        <v>6511871</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5957,11 +5953,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5992,10 +5983,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748030</v>
+        <v>122748101</v>
       </c>
       <c r="B51" t="n">
-        <v>90952</v>
+        <v>5173</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6004,38 +5995,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547653</v>
+        <v>547370</v>
       </c>
       <c r="R51" t="n">
-        <v>6511677</v>
+        <v>6511844</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6068,11 +6059,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6103,10 +6089,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748106</v>
+        <v>122748122</v>
       </c>
       <c r="B52" t="n">
-        <v>92268</v>
+        <v>92264</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6119,34 +6105,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547396</v>
+        <v>547410</v>
       </c>
       <c r="R52" t="n">
-        <v>6511793</v>
+        <v>6511972</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6209,10 +6195,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748122</v>
+        <v>122748078</v>
       </c>
       <c r="B53" t="n">
-        <v>92261</v>
+        <v>92271</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6225,34 +6211,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547410</v>
+        <v>547386</v>
       </c>
       <c r="R53" t="n">
-        <v>6511972</v>
+        <v>6511902</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6315,10 +6301,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748001</v>
+        <v>122748109</v>
       </c>
       <c r="B54" t="n">
-        <v>91174</v>
+        <v>92271</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6331,34 +6317,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1101</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547501</v>
+        <v>547448</v>
       </c>
       <c r="R54" t="n">
-        <v>6511967</v>
+        <v>6511787</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6421,10 +6407,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748070</v>
+        <v>122748005</v>
       </c>
       <c r="B55" t="n">
-        <v>90917</v>
+        <v>92271</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6433,38 +6419,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547388</v>
+        <v>547535</v>
       </c>
       <c r="R55" t="n">
-        <v>6511959</v>
+        <v>6511922</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6527,10 +6513,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122748124</v>
+        <v>122748068</v>
       </c>
       <c r="B56" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6563,14 +6549,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>547381</v>
+        <v>547411</v>
       </c>
       <c r="R56" t="n">
-        <v>6511990</v>
+        <v>6511968</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6607,7 +6593,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Större kudde</t>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6638,10 +6624,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748102</v>
+        <v>122748002</v>
       </c>
       <c r="B57" t="n">
-        <v>92268</v>
+        <v>95139</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6650,38 +6636,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547378</v>
+        <v>547505</v>
       </c>
       <c r="R57" t="n">
-        <v>6511826</v>
+        <v>6511966</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6714,6 +6700,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6744,10 +6735,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748007</v>
+        <v>122748111</v>
       </c>
       <c r="B58" t="n">
-        <v>95136</v>
+        <v>91578</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6760,34 +6751,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547554</v>
+        <v>547434</v>
       </c>
       <c r="R58" t="n">
-        <v>6511871</v>
+        <v>6511758</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6850,10 +6841,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748101</v>
+        <v>122748006</v>
       </c>
       <c r="B59" t="n">
-        <v>5173</v>
+        <v>91365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6866,34 +6857,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547370</v>
+        <v>547516</v>
       </c>
       <c r="R59" t="n">
-        <v>6511844</v>
+        <v>6511927</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6956,10 +6947,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748100</v>
+        <v>122748097</v>
       </c>
       <c r="B60" t="n">
-        <v>5173</v>
+        <v>98368</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6968,38 +6959,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547368</v>
+        <v>547426</v>
       </c>
       <c r="R60" t="n">
-        <v>6511855</v>
+        <v>6511886</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,6 +7032,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7062,10 +7067,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748123</v>
+        <v>122748079</v>
       </c>
       <c r="B61" t="n">
-        <v>91575</v>
+        <v>92262</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7074,38 +7079,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6031</v>
+        <v>5448</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547401</v>
+        <v>547387</v>
       </c>
       <c r="R61" t="n">
-        <v>6511980</v>
+        <v>6511907</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7168,10 +7173,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122747992</v>
+        <v>122748001</v>
       </c>
       <c r="B62" t="n">
-        <v>92261</v>
+        <v>91177</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7184,21 +7189,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7208,10 +7213,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547401</v>
+        <v>547501</v>
       </c>
       <c r="R62" t="n">
-        <v>6511893</v>
+        <v>6511967</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7244,11 +7249,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7279,10 +7279,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748002</v>
+        <v>122748123</v>
       </c>
       <c r="B63" t="n">
-        <v>95136</v>
+        <v>91578</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7295,34 +7295,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547505</v>
+        <v>547401</v>
       </c>
       <c r="R63" t="n">
-        <v>6511966</v>
+        <v>6511980</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7355,11 +7355,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7390,10 +7385,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748111</v>
+        <v>122748090</v>
       </c>
       <c r="B64" t="n">
-        <v>91575</v>
+        <v>92271</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7402,38 +7397,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547434</v>
+        <v>547445</v>
       </c>
       <c r="R64" t="n">
-        <v>6511758</v>
+        <v>6511922</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7496,10 +7491,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748098</v>
+        <v>122748072</v>
       </c>
       <c r="B65" t="n">
-        <v>105471</v>
+        <v>95139</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7512,34 +7507,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547433</v>
+        <v>547386</v>
       </c>
       <c r="R65" t="n">
-        <v>6511877</v>
+        <v>6511963</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7572,6 +7567,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7602,10 +7602,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748009</v>
+        <v>122748124</v>
       </c>
       <c r="B66" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7638,14 +7638,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547564</v>
+        <v>547381</v>
       </c>
       <c r="R66" t="n">
-        <v>6511874</v>
+        <v>6511990</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7678,6 +7678,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7708,10 +7713,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748006</v>
+        <v>122748100</v>
       </c>
       <c r="B67" t="n">
-        <v>91362</v>
+        <v>5173</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7724,34 +7729,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547516</v>
+        <v>547368</v>
       </c>
       <c r="R67" t="n">
-        <v>6511927</v>
+        <v>6511855</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7814,10 +7819,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748068</v>
+        <v>122748106</v>
       </c>
       <c r="B68" t="n">
-        <v>95136</v>
+        <v>92271</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7826,38 +7831,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547411</v>
+        <v>547396</v>
       </c>
       <c r="R68" t="n">
-        <v>6511968</v>
+        <v>6511793</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7890,11 +7895,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7925,10 +7925,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748077</v>
+        <v>122748081</v>
       </c>
       <c r="B69" t="n">
-        <v>79384</v>
+        <v>92271</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7941,21 +7941,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547364</v>
+        <v>547401</v>
       </c>
       <c r="R69" t="n">
-        <v>6511915</v>
+        <v>6511938</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8031,10 +8031,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748078</v>
+        <v>122748098</v>
       </c>
       <c r="B70" t="n">
-        <v>92268</v>
+        <v>105474</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8043,38 +8043,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547386</v>
+        <v>547433</v>
       </c>
       <c r="R70" t="n">
-        <v>6511902</v>
+        <v>6511877</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122748033</v>
+        <v>122748030</v>
       </c>
       <c r="B40" t="n">
-        <v>92271</v>
+        <v>90957</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4809,34 +4809,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Ängeskälen NV, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>547612</v>
+        <v>547653</v>
       </c>
       <c r="R40" t="n">
-        <v>6511812</v>
+        <v>6511677</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4869,6 +4869,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4899,10 +4904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122748077</v>
+        <v>122748101</v>
       </c>
       <c r="B41" t="n">
-        <v>79387</v>
+        <v>5173</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4911,38 +4916,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>547364</v>
+        <v>547370</v>
       </c>
       <c r="R41" t="n">
-        <v>6511915</v>
+        <v>6511844</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5005,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748030</v>
+        <v>122748077</v>
       </c>
       <c r="B42" t="n">
-        <v>90955</v>
+        <v>79389</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5021,34 +5026,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547653</v>
+        <v>547364</v>
       </c>
       <c r="R42" t="n">
-        <v>6511677</v>
+        <v>6511915</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5081,11 +5086,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tallåga som hänger mot lodyta</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5116,10 +5116,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748009</v>
+        <v>122748123</v>
       </c>
       <c r="B43" t="n">
-        <v>95139</v>
+        <v>91580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5132,34 +5132,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>6031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547564</v>
+        <v>547401</v>
       </c>
       <c r="R43" t="n">
-        <v>6511874</v>
+        <v>6511980</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5222,10 +5222,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122748110</v>
+        <v>122748081</v>
       </c>
       <c r="B44" t="n">
-        <v>92236</v>
+        <v>92273</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5234,38 +5234,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>547424</v>
+        <v>547401</v>
       </c>
       <c r="R44" t="n">
-        <v>6511755</v>
+        <v>6511938</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122748095</v>
+        <v>122748079</v>
       </c>
       <c r="B45" t="n">
-        <v>91365</v>
+        <v>92264</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5340,38 +5340,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5420</v>
+        <v>5448</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>547464</v>
+        <v>547387</v>
       </c>
       <c r="R45" t="n">
-        <v>6511904</v>
+        <v>6511907</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5434,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748070</v>
+        <v>122748009</v>
       </c>
       <c r="B46" t="n">
-        <v>90920</v>
+        <v>95141</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547388</v>
+        <v>547564</v>
       </c>
       <c r="R46" t="n">
-        <v>6511959</v>
+        <v>6511874</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122747992</v>
+        <v>122748006</v>
       </c>
       <c r="B47" t="n">
-        <v>92264</v>
+        <v>91367</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,38 +5552,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>5420</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547401</v>
+        <v>547516</v>
       </c>
       <c r="R47" t="n">
-        <v>6511893</v>
+        <v>6511927</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5616,11 +5616,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5651,10 +5646,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748103</v>
+        <v>122748109</v>
       </c>
       <c r="B48" t="n">
-        <v>98368</v>
+        <v>92273</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5663,47 +5658,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Högbrånan Ö, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547389</v>
+        <v>547448</v>
       </c>
       <c r="R48" t="n">
-        <v>6511805</v>
+        <v>6511787</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,11 +5722,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,10 +5752,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748102</v>
+        <v>122748098</v>
       </c>
       <c r="B49" t="n">
-        <v>92271</v>
+        <v>105476</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5783,38 +5764,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547378</v>
+        <v>547433</v>
       </c>
       <c r="R49" t="n">
-        <v>6511826</v>
+        <v>6511877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5877,10 +5858,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748007</v>
+        <v>122748072</v>
       </c>
       <c r="B50" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5917,10 +5898,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547554</v>
+        <v>547386</v>
       </c>
       <c r="R50" t="n">
-        <v>6511871</v>
+        <v>6511963</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5953,6 +5934,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5983,10 +5969,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748101</v>
+        <v>122748033</v>
       </c>
       <c r="B51" t="n">
-        <v>5173</v>
+        <v>92273</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5995,38 +5981,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547370</v>
+        <v>547612</v>
       </c>
       <c r="R51" t="n">
-        <v>6511844</v>
+        <v>6511812</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6089,10 +6075,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748122</v>
+        <v>122748005</v>
       </c>
       <c r="B52" t="n">
-        <v>92264</v>
+        <v>92273</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6105,34 +6091,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lerbäcken V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547410</v>
+        <v>547535</v>
       </c>
       <c r="R52" t="n">
-        <v>6511972</v>
+        <v>6511922</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6195,10 +6181,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748078</v>
+        <v>122748070</v>
       </c>
       <c r="B53" t="n">
-        <v>92271</v>
+        <v>90922</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6207,38 +6193,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547386</v>
+        <v>547388</v>
       </c>
       <c r="R53" t="n">
-        <v>6511902</v>
+        <v>6511959</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6301,10 +6287,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122748109</v>
+        <v>122748122</v>
       </c>
       <c r="B54" t="n">
-        <v>92271</v>
+        <v>92266</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6317,34 +6303,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Lerbäcken V, Ög</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>547448</v>
+        <v>547410</v>
       </c>
       <c r="R54" t="n">
-        <v>6511787</v>
+        <v>6511972</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6407,10 +6393,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122748005</v>
+        <v>122748001</v>
       </c>
       <c r="B55" t="n">
-        <v>92271</v>
+        <v>91179</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6423,34 +6409,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>1101</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>547535</v>
+        <v>547501</v>
       </c>
       <c r="R55" t="n">
-        <v>6511922</v>
+        <v>6511967</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6516,7 +6502,7 @@
         <v>122748068</v>
       </c>
       <c r="B56" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6624,10 +6610,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122748002</v>
+        <v>122748124</v>
       </c>
       <c r="B57" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6660,14 +6646,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>547505</v>
+        <v>547381</v>
       </c>
       <c r="R57" t="n">
-        <v>6511966</v>
+        <v>6511990</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6704,7 +6690,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Rikligt längs stigen</t>
+          <t>Större kudde</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6735,10 +6721,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122748111</v>
+        <v>122748078</v>
       </c>
       <c r="B58" t="n">
-        <v>91578</v>
+        <v>92273</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6747,38 +6733,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>547434</v>
+        <v>547386</v>
       </c>
       <c r="R58" t="n">
-        <v>6511758</v>
+        <v>6511902</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6841,10 +6827,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122748006</v>
+        <v>122748111</v>
       </c>
       <c r="B59" t="n">
-        <v>91365</v>
+        <v>91580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6857,34 +6843,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5420</v>
+        <v>6031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>547516</v>
+        <v>547434</v>
       </c>
       <c r="R59" t="n">
-        <v>6511927</v>
+        <v>6511758</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6947,10 +6933,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122748097</v>
+        <v>122748106</v>
       </c>
       <c r="B60" t="n">
-        <v>98368</v>
+        <v>92273</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6959,47 +6945,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>547426</v>
+        <v>547396</v>
       </c>
       <c r="R60" t="n">
-        <v>6511886</v>
+        <v>6511793</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,11 +7009,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7067,10 +7039,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122748079</v>
+        <v>122748103</v>
       </c>
       <c r="B61" t="n">
-        <v>92262</v>
+        <v>98370</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7079,38 +7051,47 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Högbrånan Ö, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>547387</v>
+        <v>547389</v>
       </c>
       <c r="R61" t="n">
-        <v>6511907</v>
+        <v>6511805</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7143,6 +7124,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>9 plantor</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7173,10 +7159,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122748001</v>
+        <v>122748102</v>
       </c>
       <c r="B62" t="n">
-        <v>91177</v>
+        <v>92273</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7189,34 +7175,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1101</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>547501</v>
+        <v>547378</v>
       </c>
       <c r="R62" t="n">
-        <v>6511967</v>
+        <v>6511826</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7279,10 +7265,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748123</v>
+        <v>122748007</v>
       </c>
       <c r="B63" t="n">
-        <v>91578</v>
+        <v>95141</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7295,34 +7281,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547401</v>
+        <v>547554</v>
       </c>
       <c r="R63" t="n">
-        <v>6511980</v>
+        <v>6511871</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7385,10 +7371,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748090</v>
+        <v>122748095</v>
       </c>
       <c r="B64" t="n">
-        <v>92271</v>
+        <v>91367</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7397,38 +7383,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547445</v>
+        <v>547464</v>
       </c>
       <c r="R64" t="n">
-        <v>6511922</v>
+        <v>6511904</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7491,10 +7477,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122748072</v>
+        <v>122747992</v>
       </c>
       <c r="B65" t="n">
-        <v>95139</v>
+        <v>92266</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7503,38 +7489,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547386</v>
+        <v>547401</v>
       </c>
       <c r="R65" t="n">
-        <v>6511963</v>
+        <v>6511893</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7571,7 +7557,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Flera lite större kuddar.</t>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7602,10 +7588,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748124</v>
+        <v>122748097</v>
       </c>
       <c r="B66" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7614,38 +7600,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547381</v>
+        <v>547426</v>
       </c>
       <c r="R66" t="n">
-        <v>6511990</v>
+        <v>6511886</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7682,7 +7677,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Större kudde</t>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7713,10 +7708,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122748100</v>
+        <v>122748002</v>
       </c>
       <c r="B67" t="n">
-        <v>5173</v>
+        <v>95141</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7729,34 +7724,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nordatbodarna V, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>547368</v>
+        <v>547505</v>
       </c>
       <c r="R67" t="n">
-        <v>6511855</v>
+        <v>6511966</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7789,6 +7784,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt längs stigen</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7819,10 +7819,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122748106</v>
+        <v>122748090</v>
       </c>
       <c r="B68" t="n">
-        <v>92271</v>
+        <v>92273</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7855,14 +7855,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>547396</v>
+        <v>547445</v>
       </c>
       <c r="R68" t="n">
-        <v>6511793</v>
+        <v>6511922</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7925,10 +7925,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122748081</v>
+        <v>122748110</v>
       </c>
       <c r="B69" t="n">
-        <v>92271</v>
+        <v>92238</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7937,38 +7937,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>547401</v>
+        <v>547424</v>
       </c>
       <c r="R69" t="n">
-        <v>6511938</v>
+        <v>6511755</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8031,10 +8031,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122748098</v>
+        <v>122748100</v>
       </c>
       <c r="B70" t="n">
-        <v>105474</v>
+        <v>5173</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8047,34 +8047,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Nordatbodarna V, Ög</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>547433</v>
+        <v>547368</v>
       </c>
       <c r="R70" t="n">
-        <v>6511877</v>
+        <v>6511855</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -5010,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122748077</v>
+        <v>122748123</v>
       </c>
       <c r="B42" t="n">
-        <v>79389</v>
+        <v>91580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5022,38 +5022,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ög</t>
+          <t>Renskinns- V, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>547364</v>
+        <v>547401</v>
       </c>
       <c r="R42" t="n">
-        <v>6511915</v>
+        <v>6511980</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122748123</v>
+        <v>122748077</v>
       </c>
       <c r="B43" t="n">
-        <v>91580</v>
+        <v>79389</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5128,38 +5128,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6031</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ög</t>
+          <t>Tretjärnarna V, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>547401</v>
+        <v>547364</v>
       </c>
       <c r="R43" t="n">
-        <v>6511980</v>
+        <v>6511915</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5434,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122748009</v>
+        <v>122748006</v>
       </c>
       <c r="B46" t="n">
-        <v>95141</v>
+        <v>91367</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5450,21 +5450,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>547564</v>
+        <v>547516</v>
       </c>
       <c r="R46" t="n">
-        <v>6511874</v>
+        <v>6511927</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122748006</v>
+        <v>122748109</v>
       </c>
       <c r="B47" t="n">
-        <v>91367</v>
+        <v>92273</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,38 +5552,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Högbrånan NÖ, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>547516</v>
+        <v>547448</v>
       </c>
       <c r="R47" t="n">
-        <v>6511927</v>
+        <v>6511787</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5646,10 +5646,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122748109</v>
+        <v>122748009</v>
       </c>
       <c r="B48" t="n">
-        <v>92273</v>
+        <v>95141</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5658,38 +5658,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Högbrånan NÖ, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>547448</v>
+        <v>547564</v>
       </c>
       <c r="R48" t="n">
-        <v>6511787</v>
+        <v>6511874</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5752,10 +5752,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122748098</v>
+        <v>122748072</v>
       </c>
       <c r="B49" t="n">
-        <v>105476</v>
+        <v>95141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5768,34 +5768,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>547433</v>
+        <v>547386</v>
       </c>
       <c r="R49" t="n">
-        <v>6511877</v>
+        <v>6511963</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5828,6 +5828,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5858,10 +5863,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122748072</v>
+        <v>122748033</v>
       </c>
       <c r="B50" t="n">
-        <v>95141</v>
+        <v>92273</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5870,38 +5875,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Buberget NV, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>547386</v>
+        <v>547612</v>
       </c>
       <c r="R50" t="n">
-        <v>6511963</v>
+        <v>6511812</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5934,11 +5939,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Flera lite större kuddar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5969,7 +5969,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122748033</v>
+        <v>122748005</v>
       </c>
       <c r="B51" t="n">
         <v>92273</v>
@@ -6005,14 +6005,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Buberget NV, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>547612</v>
+        <v>547535</v>
       </c>
       <c r="R51" t="n">
-        <v>6511812</v>
+        <v>6511922</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6075,10 +6075,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122748005</v>
+        <v>122748070</v>
       </c>
       <c r="B52" t="n">
-        <v>92273</v>
+        <v>90922</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6087,38 +6087,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>547535</v>
+        <v>547388</v>
       </c>
       <c r="R52" t="n">
-        <v>6511922</v>
+        <v>6511959</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6181,10 +6181,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122748070</v>
+        <v>122748098</v>
       </c>
       <c r="B53" t="n">
-        <v>90922</v>
+        <v>105476</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6197,34 +6197,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>547388</v>
+        <v>547433</v>
       </c>
       <c r="R53" t="n">
-        <v>6511959</v>
+        <v>6511877</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7265,10 +7265,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122748007</v>
+        <v>122748095</v>
       </c>
       <c r="B63" t="n">
-        <v>95141</v>
+        <v>91367</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7281,34 +7281,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hocklet N, Ög</t>
+          <t>Lill-Skarvhöjden V, Ög</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>547554</v>
+        <v>547464</v>
       </c>
       <c r="R63" t="n">
-        <v>6511871</v>
+        <v>6511904</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7371,10 +7371,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122748095</v>
+        <v>122748007</v>
       </c>
       <c r="B64" t="n">
-        <v>91367</v>
+        <v>95141</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7387,34 +7387,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden V, Ög</t>
+          <t>Hocklet N, Ög</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>547464</v>
+        <v>547554</v>
       </c>
       <c r="R64" t="n">
-        <v>6511904</v>
+        <v>6511871</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7477,10 +7477,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122747992</v>
+        <v>122748097</v>
       </c>
       <c r="B65" t="n">
-        <v>92266</v>
+        <v>98370</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7489,38 +7489,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Buberget V, Ög</t>
+          <t>Salaligan N, Ög</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>547401</v>
+        <v>547426</v>
       </c>
       <c r="R65" t="n">
-        <v>6511893</v>
+        <v>6511886</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7557,7 +7566,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Väster om stigen</t>
+          <t>51 plantor</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7588,10 +7597,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122748097</v>
+        <v>122747992</v>
       </c>
       <c r="B66" t="n">
-        <v>98370</v>
+        <v>92266</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7600,47 +7609,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Salaligan N, Ög</t>
+          <t>Buberget V, Ög</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>547426</v>
+        <v>547401</v>
       </c>
       <c r="R66" t="n">
-        <v>6511886</v>
+        <v>6511893</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>51 plantor</t>
+          <t>Väster om stigen</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 35003-2020 artfynd.xlsx
+++ b/artfynd/A 35003-2020 artfynd.xlsx
@@ -8140,7 +8140,7 @@
         <v>124625623</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
